--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_retail_grocery_and_food.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07357945677996255</v>
+        <v>0.07346829786640262</v>
       </c>
       <c r="C2">
-        <v>545.6842939986562</v>
+        <v>541.7788845675551</v>
       </c>
       <c r="D2">
-        <v>540.7742939986563</v>
+        <v>542.9468845675551</v>
       </c>
       <c r="E2">
-        <v>-336.7</v>
+        <v>-330.622</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.077999999999999</v>
       </c>
       <c r="G2">
         <v>4.91</v>
@@ -1445,28 +1445,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3057234</v>
       </c>
       <c r="N2">
-        <v>51.36666666666667</v>
+        <v>51.06094326666668</v>
       </c>
       <c r="O2">
-        <v>10.27333333333334</v>
+        <v>10.21218865333334</v>
       </c>
       <c r="P2">
-        <v>41.09333333333334</v>
+        <v>40.84875461333334</v>
       </c>
       <c r="Q2">
-        <v>57.89333333333334</v>
+        <v>57.64875461333334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07357945677996255</v>
+        <v>0.07380393723879053</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171841</v>
+        <v>0.5458488604849997</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>168.0167977546589</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07346829786640262</v>
+        <v>0.0733571389528427</v>
       </c>
       <c r="C3">
-        <v>541.7788845675551</v>
+        <v>537.8910025588515</v>
       </c>
       <c r="D3">
-        <v>542.9468845675551</v>
+        <v>545.1370025588515</v>
       </c>
       <c r="E3">
-        <v>-330.622</v>
+        <v>-324.544</v>
       </c>
       <c r="F3">
-        <v>6.077999999999999</v>
+        <v>12.156</v>
       </c>
       <c r="G3">
         <v>4.91</v>
@@ -1527,28 +1527,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M3">
-        <v>0.3057234</v>
+        <v>0.6114468</v>
       </c>
       <c r="N3">
-        <v>51.06094326666668</v>
+        <v>50.75521986666667</v>
       </c>
       <c r="O3">
-        <v>10.21218865333334</v>
+        <v>10.15104397333334</v>
       </c>
       <c r="P3">
-        <v>40.84875461333334</v>
+        <v>40.60417589333333</v>
       </c>
       <c r="Q3">
-        <v>57.64875461333334</v>
+        <v>57.40417589333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07380393723879053</v>
+        <v>0.07403299893147215</v>
       </c>
       <c r="T3">
-        <v>0.5458488604849997</v>
+        <v>0.5503136992276687</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>168.0167977546589</v>
+        <v>84.00839887732943</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0733571389528427</v>
+        <v>0.07324598003928277</v>
       </c>
       <c r="C4">
-        <v>537.8910025588515</v>
+        <v>534.0208609358897</v>
       </c>
       <c r="D4">
-        <v>545.1370025588515</v>
+        <v>547.3448609358898</v>
       </c>
       <c r="E4">
-        <v>-324.544</v>
+        <v>-318.466</v>
       </c>
       <c r="F4">
-        <v>12.156</v>
+        <v>18.234</v>
       </c>
       <c r="G4">
         <v>4.91</v>
@@ -1609,28 +1609,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M4">
-        <v>0.6114468</v>
+        <v>0.9171701999999998</v>
       </c>
       <c r="N4">
-        <v>50.75521986666667</v>
+        <v>50.44949646666667</v>
       </c>
       <c r="O4">
-        <v>10.15104397333334</v>
+        <v>10.08989929333334</v>
       </c>
       <c r="P4">
-        <v>40.60417589333333</v>
+        <v>40.35959717333334</v>
       </c>
       <c r="Q4">
-        <v>57.40417589333333</v>
+        <v>57.15959717333334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07403299893147215</v>
+        <v>0.07426678354565235</v>
       </c>
       <c r="T4">
-        <v>0.5503136992276687</v>
+        <v>0.5548705965011144</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>84.00839887732943</v>
+        <v>56.00559925155297</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07324598003928277</v>
+        <v>0.07313482112572285</v>
       </c>
       <c r="C5">
-        <v>534.0208609358897</v>
+        <v>530.1686761261338</v>
       </c>
       <c r="D5">
-        <v>547.3448609358898</v>
+        <v>549.5706761261339</v>
       </c>
       <c r="E5">
-        <v>-318.466</v>
+        <v>-312.388</v>
       </c>
       <c r="F5">
-        <v>18.234</v>
+        <v>24.312</v>
       </c>
       <c r="G5">
         <v>4.91</v>
@@ -1691,28 +1691,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M5">
-        <v>0.9171701999999998</v>
+        <v>1.2228936</v>
       </c>
       <c r="N5">
-        <v>50.44949646666667</v>
+        <v>50.14377306666668</v>
       </c>
       <c r="O5">
-        <v>10.08989929333334</v>
+        <v>10.02875461333334</v>
       </c>
       <c r="P5">
-        <v>40.35959717333334</v>
+        <v>40.11501845333334</v>
       </c>
       <c r="Q5">
-        <v>57.15959717333334</v>
+        <v>56.91501845333334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07426678354565235</v>
+        <v>0.07450543867262797</v>
       </c>
       <c r="T5">
-        <v>0.5548705965011144</v>
+        <v>0.5595224291344236</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>56.00559925155297</v>
+        <v>42.00419943866472</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07313482112572285</v>
+        <v>0.07302366221216293</v>
       </c>
       <c r="C6">
-        <v>530.1686761261338</v>
+        <v>526.3346680918908</v>
       </c>
       <c r="D6">
-        <v>549.5706761261339</v>
+        <v>551.8146680918908</v>
       </c>
       <c r="E6">
-        <v>-312.388</v>
+        <v>-306.31</v>
       </c>
       <c r="F6">
-        <v>24.312</v>
+        <v>30.39</v>
       </c>
       <c r="G6">
         <v>4.91</v>
@@ -1773,28 +1773,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M6">
-        <v>1.2228936</v>
+        <v>1.528617</v>
       </c>
       <c r="N6">
-        <v>50.14377306666668</v>
+        <v>49.83804966666668</v>
       </c>
       <c r="O6">
-        <v>10.02875461333334</v>
+        <v>9.967609933333335</v>
       </c>
       <c r="P6">
-        <v>40.11501845333334</v>
+        <v>39.87043973333334</v>
       </c>
       <c r="Q6">
-        <v>56.91501845333334</v>
+        <v>56.67043973333334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07450543867262797</v>
+        <v>0.07474911811806624</v>
       </c>
       <c r="T6">
-        <v>0.5595224291344236</v>
+        <v>0.5642721950863286</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.00419943866472</v>
+        <v>33.60335955093178</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07302366221216293</v>
+        <v>0.07291250329860299</v>
       </c>
       <c r="C7">
-        <v>526.3346680918908</v>
+        <v>522.5190604027731</v>
       </c>
       <c r="D7">
-        <v>551.8146680918908</v>
+        <v>554.0770604027731</v>
       </c>
       <c r="E7">
-        <v>-306.31</v>
+        <v>-300.232</v>
       </c>
       <c r="F7">
-        <v>30.39</v>
+        <v>36.468</v>
       </c>
       <c r="G7">
         <v>4.91</v>
@@ -1855,28 +1855,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M7">
-        <v>1.528617</v>
+        <v>1.8343404</v>
       </c>
       <c r="N7">
-        <v>49.83804966666668</v>
+        <v>49.53232626666667</v>
       </c>
       <c r="O7">
-        <v>9.967609933333335</v>
+        <v>9.906465253333335</v>
       </c>
       <c r="P7">
-        <v>39.87043973333334</v>
+        <v>39.62586101333333</v>
       </c>
       <c r="Q7">
-        <v>56.67043973333334</v>
+        <v>56.42586101333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07474911811806624</v>
+        <v>0.07499798223255638</v>
       </c>
       <c r="T7">
-        <v>0.5642721950863286</v>
+        <v>0.5691230198882743</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.60335955093178</v>
+        <v>28.00279962577648</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07291250329860299</v>
+        <v>0.07280134438504308</v>
       </c>
       <c r="C8">
-        <v>522.5190604027731</v>
+        <v>518.7220803099506</v>
       </c>
       <c r="D8">
-        <v>554.0770604027731</v>
+        <v>556.3580803099507</v>
       </c>
       <c r="E8">
-        <v>-300.232</v>
+        <v>-294.154</v>
       </c>
       <c r="F8">
-        <v>36.468</v>
+        <v>42.54599999999999</v>
       </c>
       <c r="G8">
         <v>4.91</v>
@@ -1937,28 +1937,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M8">
-        <v>1.8343404</v>
+        <v>2.1400638</v>
       </c>
       <c r="N8">
-        <v>49.53232626666667</v>
+        <v>49.22660286666667</v>
       </c>
       <c r="O8">
-        <v>9.906465253333335</v>
+        <v>9.845320573333336</v>
       </c>
       <c r="P8">
-        <v>39.62586101333333</v>
+        <v>39.38128229333334</v>
       </c>
       <c r="Q8">
-        <v>56.42586101333333</v>
+        <v>56.18128229333334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07499798223255638</v>
+        <v>0.07525219826348718</v>
       </c>
       <c r="T8">
-        <v>0.5691230198882743</v>
+        <v>0.5740781635031651</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.00279962577648</v>
+        <v>24.00239967923698</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07280134438504307</v>
+        <v>0.07269018547148316</v>
       </c>
       <c r="C9">
-        <v>518.7220803099508</v>
+        <v>514.9439588222474</v>
       </c>
       <c r="D9">
-        <v>556.3580803099509</v>
+        <v>558.6579588222475</v>
       </c>
       <c r="E9">
-        <v>-294.154</v>
+        <v>-288.076</v>
       </c>
       <c r="F9">
-        <v>42.546</v>
+        <v>48.624</v>
       </c>
       <c r="G9">
         <v>4.91</v>
@@ -2019,28 +2019,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M9">
-        <v>2.1400638</v>
+        <v>2.4457872</v>
       </c>
       <c r="N9">
-        <v>49.22660286666667</v>
+        <v>48.92087946666668</v>
       </c>
       <c r="O9">
-        <v>9.845320573333336</v>
+        <v>9.784175893333336</v>
       </c>
       <c r="P9">
-        <v>39.38128229333334</v>
+        <v>39.13670357333334</v>
       </c>
       <c r="Q9">
-        <v>56.18128229333334</v>
+        <v>55.93670357333334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07525219826348718</v>
+        <v>0.07551194072987299</v>
       </c>
       <c r="T9">
-        <v>0.5740781635031651</v>
+        <v>0.5791410276314229</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.00239967923698</v>
+        <v>21.00209971933236</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07269018547148316</v>
+        <v>0.07257902655792324</v>
       </c>
       <c r="C10">
-        <v>514.9439588222474</v>
+        <v>511.1849307841281</v>
       </c>
       <c r="D10">
-        <v>558.6579588222475</v>
+        <v>560.9769307841282</v>
       </c>
       <c r="E10">
-        <v>-288.076</v>
+        <v>-281.998</v>
       </c>
       <c r="F10">
-        <v>48.624</v>
+        <v>54.70199999999999</v>
       </c>
       <c r="G10">
         <v>4.91</v>
@@ -2101,28 +2101,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M10">
-        <v>2.4457872</v>
+        <v>2.7515106</v>
       </c>
       <c r="N10">
-        <v>48.92087946666668</v>
+        <v>48.61515606666667</v>
       </c>
       <c r="O10">
-        <v>9.784175893333336</v>
+        <v>9.723031213333336</v>
       </c>
       <c r="P10">
-        <v>39.13670357333334</v>
+        <v>38.89212485333334</v>
       </c>
       <c r="Q10">
-        <v>55.93670357333334</v>
+        <v>55.69212485333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07551194072987299</v>
+        <v>0.07577739182189366</v>
       </c>
       <c r="T10">
-        <v>0.5791410276314229</v>
+        <v>0.5843151634987634</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.00209971933236</v>
+        <v>18.66853308385098</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07257902655792324</v>
+        <v>0.0724678676443633</v>
       </c>
       <c r="C11">
-        <v>511.1849307841281</v>
+        <v>507.4452349556404</v>
       </c>
       <c r="D11">
-        <v>560.9769307841282</v>
+        <v>563.3152349556404</v>
       </c>
       <c r="E11">
-        <v>-281.998</v>
+        <v>-275.92</v>
       </c>
       <c r="F11">
-        <v>54.70199999999999</v>
+        <v>60.77999999999999</v>
       </c>
       <c r="G11">
         <v>4.91</v>
@@ -2183,28 +2183,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M11">
-        <v>2.7515106</v>
+        <v>3.057233999999999</v>
       </c>
       <c r="N11">
-        <v>48.61515606666667</v>
+        <v>48.30943266666667</v>
       </c>
       <c r="O11">
-        <v>9.723031213333336</v>
+        <v>9.661886533333336</v>
       </c>
       <c r="P11">
-        <v>38.89212485333334</v>
+        <v>38.64754613333334</v>
       </c>
       <c r="Q11">
-        <v>55.69212485333333</v>
+        <v>55.44754613333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07577739182189366</v>
+        <v>0.07604874182707033</v>
       </c>
       <c r="T11">
-        <v>0.5843151634987634</v>
+        <v>0.5896042801631559</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.66853308385098</v>
+        <v>16.80167977546589</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0724678676443633</v>
+        <v>0.07235670873080337</v>
       </c>
       <c r="C12">
-        <v>507.4452349556404</v>
+        <v>503.7251140943605</v>
       </c>
       <c r="D12">
-        <v>563.3152349556404</v>
+        <v>565.6731140943606</v>
       </c>
       <c r="E12">
-        <v>-275.92</v>
+        <v>-269.842</v>
       </c>
       <c r="F12">
-        <v>60.78</v>
+        <v>66.85799999999999</v>
       </c>
       <c r="G12">
         <v>4.91</v>
@@ -2265,28 +2265,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M12">
-        <v>3.057234</v>
+        <v>3.3629574</v>
       </c>
       <c r="N12">
-        <v>48.30943266666667</v>
+        <v>48.00370926666668</v>
       </c>
       <c r="O12">
-        <v>9.661886533333336</v>
+        <v>9.600741853333336</v>
       </c>
       <c r="P12">
-        <v>38.64754613333334</v>
+        <v>38.40296741333334</v>
       </c>
       <c r="Q12">
-        <v>55.44754613333333</v>
+        <v>55.20296741333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07604874182707033</v>
+        <v>0.07632618958517233</v>
       </c>
       <c r="T12">
-        <v>0.589604280163156</v>
+        <v>0.5950122533818044</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.80167977546589</v>
+        <v>15.27425434133263</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07235670873080337</v>
+        <v>0.07224554981724345</v>
       </c>
       <c r="C13">
-        <v>503.7251140943605</v>
+        <v>500.0248150394091</v>
       </c>
       <c r="D13">
-        <v>565.6731140943606</v>
+        <v>568.0508150394091</v>
       </c>
       <c r="E13">
-        <v>-269.842</v>
+        <v>-263.764</v>
       </c>
       <c r="F13">
-        <v>66.85799999999999</v>
+        <v>72.93599999999999</v>
       </c>
       <c r="G13">
         <v>4.91</v>
@@ -2347,28 +2347,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M13">
-        <v>3.3629574</v>
+        <v>3.668680799999999</v>
       </c>
       <c r="N13">
-        <v>48.00370926666668</v>
+        <v>47.69798586666668</v>
       </c>
       <c r="O13">
-        <v>9.600741853333336</v>
+        <v>9.539597173333336</v>
       </c>
       <c r="P13">
-        <v>38.40296741333334</v>
+        <v>38.15838869333334</v>
       </c>
       <c r="Q13">
-        <v>55.20296741333334</v>
+        <v>54.95838869333334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07632618958517233</v>
+        <v>0.07660994297414028</v>
       </c>
       <c r="T13">
-        <v>0.5950122533818044</v>
+        <v>0.6005431350826951</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.27425434133263</v>
+        <v>14.00139981288824</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07224554981724345</v>
+        <v>0.07213439090368354</v>
       </c>
       <c r="C14">
-        <v>500.0248150394091</v>
+        <v>496.3445887975926</v>
       </c>
       <c r="D14">
-        <v>568.0508150394091</v>
+        <v>570.4485887975926</v>
       </c>
       <c r="E14">
-        <v>-263.764</v>
+        <v>-257.686</v>
       </c>
       <c r="F14">
-        <v>72.93599999999999</v>
+        <v>79.014</v>
       </c>
       <c r="G14">
         <v>4.91</v>
@@ -2429,28 +2429,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M14">
-        <v>3.668680799999999</v>
+        <v>3.974404199999999</v>
       </c>
       <c r="N14">
-        <v>47.69798586666668</v>
+        <v>47.39226246666667</v>
       </c>
       <c r="O14">
-        <v>9.539597173333336</v>
+        <v>9.478452493333334</v>
       </c>
       <c r="P14">
-        <v>38.15838869333334</v>
+        <v>37.91380997333334</v>
       </c>
       <c r="Q14">
-        <v>54.95838869333334</v>
+        <v>54.71380997333333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07660994297414028</v>
+        <v>0.0769002194295213</v>
       </c>
       <c r="T14">
-        <v>0.6005431350826951</v>
+        <v>0.6062011634893532</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.00139981288824</v>
+        <v>12.92436905805068</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07213439090368354</v>
+        <v>0.07219123199012362</v>
       </c>
       <c r="C15">
-        <v>496.3445887975926</v>
+        <v>489.037964171141</v>
       </c>
       <c r="D15">
-        <v>570.4485887975926</v>
+        <v>569.219964171141</v>
       </c>
       <c r="E15">
-        <v>-257.686</v>
+        <v>-251.608</v>
       </c>
       <c r="F15">
-        <v>79.014</v>
+        <v>85.092</v>
       </c>
       <c r="G15">
         <v>4.91</v>
@@ -2511,45 +2511,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M15">
-        <v>3.974404199999999</v>
+        <v>4.407765599999999</v>
       </c>
       <c r="N15">
-        <v>47.39226246666667</v>
+        <v>46.95890106666668</v>
       </c>
       <c r="O15">
-        <v>9.478452493333334</v>
+        <v>9.391780213333336</v>
       </c>
       <c r="P15">
-        <v>37.91380997333334</v>
+        <v>37.56712085333334</v>
       </c>
       <c r="Q15">
-        <v>54.71380997333333</v>
+        <v>54.36712085333334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0769002194295213</v>
+        <v>0.07719724650014373</v>
       </c>
       <c r="T15">
-        <v>0.6062011634893532</v>
+        <v>0.6119907739519801</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>12.92436905805068</v>
+        <v>11.65367474773765</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07219123199012362</v>
+        <v>0.07209207307656366</v>
       </c>
       <c r="C16">
-        <v>489.037964171141</v>
+        <v>485.1067417591798</v>
       </c>
       <c r="D16">
-        <v>569.219964171141</v>
+        <v>571.3667417591798</v>
       </c>
       <c r="E16">
-        <v>-251.608</v>
+        <v>-245.53</v>
       </c>
       <c r="F16">
-        <v>85.092</v>
+        <v>91.17</v>
       </c>
       <c r="G16">
         <v>4.91</v>
@@ -2593,28 +2593,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M16">
-        <v>4.407765599999999</v>
+        <v>4.722606</v>
       </c>
       <c r="N16">
-        <v>46.95890106666668</v>
+        <v>46.64406066666668</v>
       </c>
       <c r="O16">
-        <v>9.391780213333336</v>
+        <v>9.328812133333335</v>
       </c>
       <c r="P16">
-        <v>37.56712085333334</v>
+        <v>37.31524853333334</v>
       </c>
       <c r="Q16">
-        <v>54.36712085333334</v>
+        <v>54.11524853333334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07719724650014373</v>
+        <v>0.07750126244301608</v>
       </c>
       <c r="T16">
-        <v>0.6119907739519801</v>
+        <v>0.6179166105431394</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.65367474773765</v>
+        <v>10.87676309788847</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07209207307656366</v>
+        <v>0.07199291416300374</v>
       </c>
       <c r="C17">
-        <v>485.1067417591798</v>
+        <v>481.1917735243562</v>
       </c>
       <c r="D17">
-        <v>571.3667417591798</v>
+        <v>573.5297735243562</v>
       </c>
       <c r="E17">
-        <v>-245.53</v>
+        <v>-239.452</v>
       </c>
       <c r="F17">
-        <v>91.16999999999999</v>
+        <v>97.24799999999999</v>
       </c>
       <c r="G17">
         <v>4.91</v>
@@ -2675,28 +2675,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M17">
-        <v>4.722605999999999</v>
+        <v>5.037446399999999</v>
       </c>
       <c r="N17">
-        <v>46.64406066666668</v>
+        <v>46.32922026666667</v>
       </c>
       <c r="O17">
-        <v>9.328812133333335</v>
+        <v>9.265844053333335</v>
       </c>
       <c r="P17">
-        <v>37.31524853333334</v>
+        <v>37.06337621333334</v>
       </c>
       <c r="Q17">
-        <v>54.11524853333334</v>
+        <v>53.86337621333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07750126244301608</v>
+        <v>0.07781251686071874</v>
       </c>
       <c r="T17">
-        <v>0.6179166105431394</v>
+        <v>0.6239835384817073</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.87676309788847</v>
+        <v>10.19696540427044</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07199291416300374</v>
+        <v>0.07212495524944383</v>
       </c>
       <c r="C18">
-        <v>481.1917735243562</v>
+        <v>472.2370546967526</v>
       </c>
       <c r="D18">
-        <v>573.5297735243562</v>
+        <v>570.6530546967526</v>
       </c>
       <c r="E18">
-        <v>-239.452</v>
+        <v>-233.374</v>
       </c>
       <c r="F18">
-        <v>97.24799999999999</v>
+        <v>103.326</v>
       </c>
       <c r="G18">
         <v>4.91</v>
@@ -2757,45 +2757,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M18">
-        <v>5.037446399999999</v>
+        <v>5.527940999999999</v>
       </c>
       <c r="N18">
-        <v>46.32922026666667</v>
+        <v>45.83872566666668</v>
       </c>
       <c r="O18">
-        <v>9.265844053333335</v>
+        <v>9.167745133333336</v>
       </c>
       <c r="P18">
-        <v>37.06337621333334</v>
+        <v>36.67098053333334</v>
       </c>
       <c r="Q18">
-        <v>53.86337621333334</v>
+        <v>53.47098053333334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07781251686071874</v>
+        <v>0.07813127138487208</v>
       </c>
       <c r="T18">
-        <v>0.6239835384817073</v>
+        <v>0.6301966574549395</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.19696540427044</v>
+        <v>9.292187935194439</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07212495524944383</v>
+        <v>0.07203939633588391</v>
       </c>
       <c r="C19">
-        <v>472.2370546967526</v>
+        <v>468.0197855898919</v>
       </c>
       <c r="D19">
-        <v>570.6530546967526</v>
+        <v>572.5137855898919</v>
       </c>
       <c r="E19">
-        <v>-233.374</v>
+        <v>-227.296</v>
       </c>
       <c r="F19">
-        <v>103.326</v>
+        <v>109.404</v>
       </c>
       <c r="G19">
         <v>4.91</v>
@@ -2839,28 +2839,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M19">
-        <v>5.527940999999999</v>
+        <v>5.853114000000001</v>
       </c>
       <c r="N19">
-        <v>45.83872566666668</v>
+        <v>45.51355266666668</v>
       </c>
       <c r="O19">
-        <v>9.167745133333336</v>
+        <v>9.102710533333335</v>
       </c>
       <c r="P19">
-        <v>36.67098053333334</v>
+        <v>36.41084213333334</v>
       </c>
       <c r="Q19">
-        <v>53.47098053333334</v>
+        <v>53.21084213333334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07813127138487208</v>
+        <v>0.07845780040961453</v>
       </c>
       <c r="T19">
-        <v>0.6301966574549395</v>
+        <v>0.6365613159153238</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.292187935194439</v>
+        <v>8.77595527212808</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0720393963358839</v>
+        <v>0.07195383742232397</v>
       </c>
       <c r="C20">
-        <v>468.0197855898922</v>
+        <v>463.8146907663746</v>
       </c>
       <c r="D20">
-        <v>572.5137855898922</v>
+        <v>574.3866907663746</v>
       </c>
       <c r="E20">
-        <v>-227.296</v>
+        <v>-221.218</v>
       </c>
       <c r="F20">
-        <v>109.404</v>
+        <v>115.482</v>
       </c>
       <c r="G20">
         <v>4.91</v>
@@ -2921,28 +2921,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M20">
-        <v>5.853113999999999</v>
+        <v>6.178287</v>
       </c>
       <c r="N20">
-        <v>45.51355266666668</v>
+        <v>45.18837966666668</v>
       </c>
       <c r="O20">
-        <v>9.102710533333335</v>
+        <v>9.037675933333336</v>
       </c>
       <c r="P20">
-        <v>36.41084213333334</v>
+        <v>36.15070373333334</v>
       </c>
       <c r="Q20">
-        <v>53.21084213333334</v>
+        <v>52.95070373333334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0784578004096145</v>
+        <v>0.07879239187941231</v>
       </c>
       <c r="T20">
-        <v>0.6365613159153236</v>
+        <v>0.6430831264364582</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.775955272128082</v>
+        <v>8.314062889384498</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07195383742232397</v>
+        <v>0.07186827850876405</v>
       </c>
       <c r="C21">
-        <v>463.8146907663746</v>
+        <v>459.6218900981497</v>
       </c>
       <c r="D21">
-        <v>574.3866907663746</v>
+        <v>576.2718900981497</v>
       </c>
       <c r="E21">
-        <v>-221.218</v>
+        <v>-215.14</v>
       </c>
       <c r="F21">
-        <v>115.482</v>
+        <v>121.56</v>
       </c>
       <c r="G21">
         <v>4.91</v>
@@ -3003,28 +3003,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M21">
-        <v>6.178287</v>
+        <v>6.50346</v>
       </c>
       <c r="N21">
-        <v>45.18837966666668</v>
+        <v>44.86320666666668</v>
       </c>
       <c r="O21">
-        <v>9.037675933333336</v>
+        <v>8.972641333333335</v>
       </c>
       <c r="P21">
-        <v>36.15070373333334</v>
+        <v>35.89056533333334</v>
       </c>
       <c r="Q21">
-        <v>52.95070373333334</v>
+        <v>52.69056533333334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07879239187941231</v>
+        <v>0.07913534813595506</v>
       </c>
       <c r="T21">
-        <v>0.6430831264364582</v>
+        <v>0.6497679822206208</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.314062889384498</v>
+        <v>7.898359744915273</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07186827850876405</v>
+        <v>0.07191711959520414</v>
       </c>
       <c r="C22">
-        <v>459.6218900981497</v>
+        <v>452.4662159275859</v>
       </c>
       <c r="D22">
-        <v>576.2718900981497</v>
+        <v>575.194215927586</v>
       </c>
       <c r="E22">
-        <v>-215.14</v>
+        <v>-209.062</v>
       </c>
       <c r="F22">
-        <v>121.56</v>
+        <v>127.638</v>
       </c>
       <c r="G22">
         <v>4.91</v>
@@ -3085,45 +3085,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M22">
-        <v>6.50346</v>
+        <v>6.930743400000001</v>
       </c>
       <c r="N22">
-        <v>44.86320666666668</v>
+        <v>44.43592326666668</v>
       </c>
       <c r="O22">
-        <v>8.972641333333335</v>
+        <v>8.887184653333335</v>
       </c>
       <c r="P22">
-        <v>35.89056533333334</v>
+        <v>35.54873861333334</v>
       </c>
       <c r="Q22">
-        <v>52.69056533333334</v>
+        <v>52.34873861333334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07913534813595506</v>
+        <v>0.07948698682937232</v>
       </c>
       <c r="T22">
-        <v>0.6497679822206208</v>
+        <v>0.656622074860079</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.898359744915273</v>
+        <v>7.411422368726949</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07191711959520414</v>
+        <v>0.07183796068164421</v>
       </c>
       <c r="C23">
-        <v>452.466215927586</v>
+        <v>448.1368839502273</v>
       </c>
       <c r="D23">
-        <v>575.194215927586</v>
+        <v>576.9428839502274</v>
       </c>
       <c r="E23">
-        <v>-209.062</v>
+        <v>-202.984</v>
       </c>
       <c r="F23">
-        <v>127.638</v>
+        <v>133.716</v>
       </c>
       <c r="G23">
         <v>4.91</v>
@@ -3167,28 +3167,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M23">
-        <v>6.9307434</v>
+        <v>7.260778799999999</v>
       </c>
       <c r="N23">
-        <v>44.43592326666668</v>
+        <v>44.10588786666668</v>
       </c>
       <c r="O23">
-        <v>8.887184653333335</v>
+        <v>8.821177573333335</v>
       </c>
       <c r="P23">
-        <v>35.54873861333334</v>
+        <v>35.28471029333334</v>
       </c>
       <c r="Q23">
-        <v>52.34873861333334</v>
+        <v>52.08471029333334</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07948698682937232</v>
+        <v>0.07984764189954385</v>
       </c>
       <c r="T23">
-        <v>0.656622074860079</v>
+        <v>0.6636519134646512</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.41142236872695</v>
+        <v>7.074539533784817</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07183796068164421</v>
+        <v>0.07175880176808427</v>
       </c>
       <c r="C24">
-        <v>448.1368839502273</v>
+        <v>443.8182167687314</v>
       </c>
       <c r="D24">
-        <v>576.9428839502274</v>
+        <v>578.7022167687314</v>
       </c>
       <c r="E24">
-        <v>-202.984</v>
+        <v>-196.906</v>
       </c>
       <c r="F24">
-        <v>133.716</v>
+        <v>139.794</v>
       </c>
       <c r="G24">
         <v>4.91</v>
@@ -3249,28 +3249,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M24">
-        <v>7.260778799999999</v>
+        <v>7.5908142</v>
       </c>
       <c r="N24">
-        <v>44.10588786666668</v>
+        <v>43.77585246666668</v>
       </c>
       <c r="O24">
-        <v>8.821177573333335</v>
+        <v>8.755170493333337</v>
       </c>
       <c r="P24">
-        <v>35.28471029333334</v>
+        <v>35.02068197333334</v>
       </c>
       <c r="Q24">
-        <v>52.08471029333334</v>
+        <v>51.82068197333334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07984764189954385</v>
+        <v>0.08021766463387568</v>
       </c>
       <c r="T24">
-        <v>0.6636519134646512</v>
+        <v>0.6708643452797319</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.074539533784817</v>
+        <v>6.766950858402868</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07175880176808427</v>
+        <v>0.07167964285452436</v>
       </c>
       <c r="C25">
-        <v>443.8182167687314</v>
+        <v>439.5103122453821</v>
       </c>
       <c r="D25">
-        <v>578.7022167687314</v>
+        <v>580.4723122453821</v>
       </c>
       <c r="E25">
-        <v>-196.906</v>
+        <v>-190.828</v>
       </c>
       <c r="F25">
-        <v>139.794</v>
+        <v>145.872</v>
       </c>
       <c r="G25">
         <v>4.91</v>
@@ -3331,28 +3331,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M25">
-        <v>7.5908142</v>
+        <v>7.920849600000001</v>
       </c>
       <c r="N25">
-        <v>43.77585246666668</v>
+        <v>43.44581706666667</v>
       </c>
       <c r="O25">
-        <v>8.755170493333337</v>
+        <v>8.689163413333334</v>
       </c>
       <c r="P25">
-        <v>35.02068197333334</v>
+        <v>34.75665365333334</v>
       </c>
       <c r="Q25">
-        <v>51.82068197333334</v>
+        <v>51.55665365333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08021766463387568</v>
+        <v>0.08059742480858467</v>
       </c>
       <c r="T25">
-        <v>0.6708643452797319</v>
+        <v>0.6782665779320517</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.766950858402868</v>
+        <v>6.484994572636079</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07167964285452436</v>
+        <v>0.07160048394096444</v>
       </c>
       <c r="C26">
-        <v>439.5103122453821</v>
+        <v>435.2132694434758</v>
       </c>
       <c r="D26">
-        <v>580.4723122453821</v>
+        <v>582.2532694434758</v>
       </c>
       <c r="E26">
-        <v>-190.828</v>
+        <v>-184.75</v>
       </c>
       <c r="F26">
-        <v>145.872</v>
+        <v>151.95</v>
       </c>
       <c r="G26">
         <v>4.91</v>
@@ -3413,28 +3413,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M26">
-        <v>7.920849599999999</v>
+        <v>8.250885</v>
       </c>
       <c r="N26">
-        <v>43.44581706666668</v>
+        <v>43.11578166666668</v>
       </c>
       <c r="O26">
-        <v>8.689163413333336</v>
+        <v>8.623156333333336</v>
       </c>
       <c r="P26">
-        <v>34.75665365333334</v>
+        <v>34.49262533333334</v>
       </c>
       <c r="Q26">
-        <v>51.55665365333334</v>
+        <v>51.29262533333334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08059742480858467</v>
+        <v>0.0809873119212859</v>
       </c>
       <c r="T26">
-        <v>0.6782665779320516</v>
+        <v>0.6858662034550997</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.484994572636082</v>
+        <v>6.225594789730638</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07160048394096444</v>
+        <v>0.07172932502740449</v>
       </c>
       <c r="C27">
-        <v>435.2132694434758</v>
+        <v>426.2420917869387</v>
       </c>
       <c r="D27">
-        <v>582.2532694434758</v>
+        <v>579.3600917869387</v>
       </c>
       <c r="E27">
-        <v>-184.75</v>
+        <v>-178.672</v>
       </c>
       <c r="F27">
-        <v>151.95</v>
+        <v>158.028</v>
       </c>
       <c r="G27">
         <v>4.91</v>
@@ -3495,45 +3495,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M27">
-        <v>8.250885</v>
+        <v>8.7389484</v>
       </c>
       <c r="N27">
-        <v>43.11578166666668</v>
+        <v>42.62771826666668</v>
       </c>
       <c r="O27">
-        <v>8.623156333333336</v>
+        <v>8.525543653333335</v>
       </c>
       <c r="P27">
-        <v>34.49262533333334</v>
+        <v>34.10217461333334</v>
       </c>
       <c r="Q27">
-        <v>51.29262533333334</v>
+        <v>50.90217461333334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0809873119212859</v>
+        <v>0.08138773652351959</v>
       </c>
       <c r="T27">
-        <v>0.6858662034550997</v>
+        <v>0.6936712242625547</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.225594789730638</v>
+        <v>5.877900213561928</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07172932502740449</v>
+        <v>0.07165816611384458</v>
       </c>
       <c r="C28">
-        <v>426.2420917869387</v>
+        <v>421.7584289301848</v>
       </c>
       <c r="D28">
-        <v>579.3600917869387</v>
+        <v>580.9544289301848</v>
       </c>
       <c r="E28">
-        <v>-178.672</v>
+        <v>-172.594</v>
       </c>
       <c r="F28">
-        <v>158.028</v>
+        <v>164.106</v>
       </c>
       <c r="G28">
         <v>4.91</v>
@@ -3577,28 +3577,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M28">
-        <v>8.7389484</v>
+        <v>9.0750618</v>
       </c>
       <c r="N28">
-        <v>42.62771826666668</v>
+        <v>42.29160486666667</v>
       </c>
       <c r="O28">
-        <v>8.525543653333335</v>
+        <v>8.458320973333334</v>
       </c>
       <c r="P28">
-        <v>34.10217461333334</v>
+        <v>33.83328389333334</v>
       </c>
       <c r="Q28">
-        <v>50.90217461333334</v>
+        <v>50.63328389333333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08138773652351959</v>
+        <v>0.0817991316628008</v>
       </c>
       <c r="T28">
-        <v>0.6936712242625547</v>
+        <v>0.7016900812565153</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.877900213561928</v>
+        <v>5.660200205652227</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07165816611384458</v>
+        <v>0.07158700720028464</v>
       </c>
       <c r="C29">
-        <v>421.7584289301848</v>
+        <v>417.2835651789718</v>
       </c>
       <c r="D29">
-        <v>580.9544289301848</v>
+        <v>582.5575651789718</v>
       </c>
       <c r="E29">
-        <v>-172.594</v>
+        <v>-166.516</v>
       </c>
       <c r="F29">
-        <v>164.106</v>
+        <v>170.184</v>
       </c>
       <c r="G29">
         <v>4.91</v>
@@ -3659,28 +3659,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M29">
-        <v>9.0750618</v>
+        <v>9.411175200000001</v>
       </c>
       <c r="N29">
-        <v>42.29160486666667</v>
+        <v>41.95549146666667</v>
       </c>
       <c r="O29">
-        <v>8.458320973333334</v>
+        <v>8.391098293333334</v>
       </c>
       <c r="P29">
-        <v>33.83328389333334</v>
+        <v>33.56439317333334</v>
       </c>
       <c r="Q29">
-        <v>50.63328389333333</v>
+        <v>50.36439317333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0817991316628008</v>
+        <v>0.08222195444483979</v>
       </c>
       <c r="T29">
-        <v>0.7016900812565153</v>
+        <v>0.7099316842780857</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.660200205652227</v>
+        <v>5.458050198307505</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07158700720028464</v>
+        <v>0.07151584828672472</v>
       </c>
       <c r="C30">
-        <v>417.2835651789718</v>
+        <v>412.8175735779188</v>
       </c>
       <c r="D30">
-        <v>582.5575651789718</v>
+        <v>584.1695735779189</v>
       </c>
       <c r="E30">
-        <v>-166.516</v>
+        <v>-160.438</v>
       </c>
       <c r="F30">
-        <v>170.184</v>
+        <v>176.262</v>
       </c>
       <c r="G30">
         <v>4.91</v>
@@ -3741,28 +3741,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M30">
-        <v>9.411175200000001</v>
+        <v>9.747288600000001</v>
       </c>
       <c r="N30">
-        <v>41.95549146666667</v>
+        <v>41.61937806666667</v>
       </c>
       <c r="O30">
-        <v>8.391098293333334</v>
+        <v>8.323875613333334</v>
       </c>
       <c r="P30">
-        <v>33.56439317333334</v>
+        <v>33.29550245333333</v>
       </c>
       <c r="Q30">
-        <v>50.36439317333333</v>
+        <v>50.09550245333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08222195444483979</v>
+        <v>0.0826566877277813</v>
       </c>
       <c r="T30">
-        <v>0.7099316842780857</v>
+        <v>0.7184054451312498</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.458050198307505</v>
+        <v>5.26984157077966</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07151584828672472</v>
+        <v>0.07144468937316481</v>
       </c>
       <c r="C31">
-        <v>412.8175735779189</v>
+        <v>408.3605279823835</v>
       </c>
       <c r="D31">
-        <v>584.1695735779189</v>
+        <v>585.7905279823835</v>
       </c>
       <c r="E31">
-        <v>-160.438</v>
+        <v>-154.36</v>
       </c>
       <c r="F31">
-        <v>176.262</v>
+        <v>182.34</v>
       </c>
       <c r="G31">
         <v>4.91</v>
@@ -3823,28 +3823,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M31">
-        <v>9.747288599999999</v>
+        <v>10.083402</v>
       </c>
       <c r="N31">
-        <v>41.61937806666668</v>
+        <v>41.28326466666667</v>
       </c>
       <c r="O31">
-        <v>8.323875613333335</v>
+        <v>8.256652933333335</v>
       </c>
       <c r="P31">
-        <v>33.29550245333334</v>
+        <v>33.02661173333334</v>
       </c>
       <c r="Q31">
-        <v>50.09550245333334</v>
+        <v>49.82661173333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0826566877277813</v>
+        <v>0.08310384196166401</v>
       </c>
       <c r="T31">
-        <v>0.7184054451312498</v>
+        <v>0.7271213134373615</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.26984157077966</v>
+        <v>5.094180185087005</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07144468937316481</v>
+        <v>0.07137353045960487</v>
       </c>
       <c r="C32">
-        <v>408.3605279823835</v>
+        <v>403.9125030697409</v>
       </c>
       <c r="D32">
-        <v>585.7905279823835</v>
+        <v>587.4205030697409</v>
       </c>
       <c r="E32">
-        <v>-154.36</v>
+        <v>-148.282</v>
       </c>
       <c r="F32">
-        <v>182.34</v>
+        <v>188.418</v>
       </c>
       <c r="G32">
         <v>4.91</v>
@@ -3905,28 +3905,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M32">
-        <v>10.083402</v>
+        <v>10.4195154</v>
       </c>
       <c r="N32">
-        <v>41.28326466666667</v>
+        <v>40.94715126666667</v>
       </c>
       <c r="O32">
-        <v>8.256652933333335</v>
+        <v>8.189430253333335</v>
       </c>
       <c r="P32">
-        <v>33.02661173333334</v>
+        <v>32.75772101333334</v>
       </c>
       <c r="Q32">
-        <v>49.82661173333334</v>
+        <v>49.55772101333334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08310384196166401</v>
+        <v>0.08356395718783316</v>
       </c>
       <c r="T32">
-        <v>0.7271213134373615</v>
+        <v>0.7360898156074184</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.094180185087005</v>
+        <v>4.929851792019682</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07137353045960487</v>
+        <v>0.07130237154604495</v>
       </c>
       <c r="C33">
-        <v>403.9125030697409</v>
+        <v>399.4735743508488</v>
       </c>
       <c r="D33">
-        <v>587.4205030697409</v>
+        <v>589.0595743508488</v>
       </c>
       <c r="E33">
-        <v>-148.282</v>
+        <v>-142.204</v>
       </c>
       <c r="F33">
-        <v>188.418</v>
+        <v>194.496</v>
       </c>
       <c r="G33">
         <v>4.91</v>
@@ -3987,28 +3987,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M33">
-        <v>10.4195154</v>
+        <v>10.7556288</v>
       </c>
       <c r="N33">
-        <v>40.94715126666667</v>
+        <v>40.61103786666668</v>
       </c>
       <c r="O33">
-        <v>8.189430253333335</v>
+        <v>8.122207573333336</v>
       </c>
       <c r="P33">
-        <v>32.75772101333334</v>
+        <v>32.48883029333334</v>
       </c>
       <c r="Q33">
-        <v>49.55772101333334</v>
+        <v>49.28883029333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08356395718783316</v>
+        <v>0.08403760521477199</v>
       </c>
       <c r="T33">
-        <v>0.7360898156074184</v>
+        <v>0.7453220972530651</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.929851792019682</v>
+        <v>4.775793923519068</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07130237154604495</v>
+        <v>0.07123121263248502</v>
       </c>
       <c r="C34">
-        <v>399.4735743508488</v>
+        <v>395.0438181817126</v>
       </c>
       <c r="D34">
-        <v>589.0595743508488</v>
+        <v>590.7078181817126</v>
       </c>
       <c r="E34">
-        <v>-142.204</v>
+        <v>-136.126</v>
       </c>
       <c r="F34">
-        <v>194.496</v>
+        <v>200.574</v>
       </c>
       <c r="G34">
         <v>4.91</v>
@@ -4069,28 +4069,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M34">
-        <v>10.7556288</v>
+        <v>11.0917422</v>
       </c>
       <c r="N34">
-        <v>40.61103786666668</v>
+        <v>40.27492446666668</v>
       </c>
       <c r="O34">
-        <v>8.122207573333336</v>
+        <v>8.054984893333335</v>
       </c>
       <c r="P34">
-        <v>32.48883029333334</v>
+        <v>32.21993957333334</v>
       </c>
       <c r="Q34">
-        <v>49.28883029333334</v>
+        <v>49.01993957333334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08403760521477199</v>
+        <v>0.08452539198878362</v>
       </c>
       <c r="T34">
-        <v>0.7453220972530651</v>
+        <v>0.7548299693955969</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.775793923519068</v>
+        <v>4.631072895533642</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07123121263248502</v>
+        <v>0.0718400537189251</v>
       </c>
       <c r="C35">
-        <v>395.0438181817126</v>
+        <v>375.1545106601378</v>
       </c>
       <c r="D35">
-        <v>590.7078181817126</v>
+        <v>576.8965106601378</v>
       </c>
       <c r="E35">
-        <v>-136.126</v>
+        <v>-130.048</v>
       </c>
       <c r="F35">
-        <v>200.574</v>
+        <v>206.652</v>
       </c>
       <c r="G35">
         <v>4.91</v>
@@ -4151,45 +4151,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M35">
-        <v>11.0917422</v>
+        <v>11.9444856</v>
       </c>
       <c r="N35">
-        <v>40.27492446666668</v>
+        <v>39.42218106666667</v>
       </c>
       <c r="O35">
-        <v>8.054984893333335</v>
+        <v>7.884436213333335</v>
       </c>
       <c r="P35">
-        <v>32.21993957333334</v>
+        <v>31.53774485333334</v>
       </c>
       <c r="Q35">
-        <v>49.01993957333334</v>
+        <v>48.33774485333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08452539198878362</v>
+        <v>0.08502796018018954</v>
       </c>
       <c r="T35">
-        <v>0.7548299693955969</v>
+        <v>0.7646259588757811</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.631072895533642</v>
+        <v>4.300450298727529</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0718400537189251</v>
+        <v>0.07178889480536517</v>
       </c>
       <c r="C36">
-        <v>375.1545106601378</v>
+        <v>370.2121264276768</v>
       </c>
       <c r="D36">
-        <v>576.8965106601378</v>
+        <v>578.0321264276769</v>
       </c>
       <c r="E36">
-        <v>-130.048</v>
+        <v>-123.97</v>
       </c>
       <c r="F36">
-        <v>206.652</v>
+        <v>212.73</v>
       </c>
       <c r="G36">
         <v>4.91</v>
@@ -4233,28 +4233,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M36">
-        <v>11.9444856</v>
+        <v>12.295794</v>
       </c>
       <c r="N36">
-        <v>39.42218106666667</v>
+        <v>39.07087266666667</v>
       </c>
       <c r="O36">
-        <v>7.884436213333335</v>
+        <v>7.814174533333335</v>
       </c>
       <c r="P36">
-        <v>31.53774485333334</v>
+        <v>31.25669813333334</v>
       </c>
       <c r="Q36">
-        <v>48.33774485333333</v>
+        <v>48.05669813333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08502796018018954</v>
+        <v>0.08554599200825411</v>
       </c>
       <c r="T36">
-        <v>0.7646259588757811</v>
+        <v>0.7747233634168941</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.300450298727529</v>
+        <v>4.177580290192457</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07178889480536517</v>
+        <v>0.07173773589180525</v>
       </c>
       <c r="C37">
-        <v>370.2121264276768</v>
+        <v>365.2742219130392</v>
       </c>
       <c r="D37">
-        <v>578.0321264276769</v>
+        <v>579.1722219130393</v>
       </c>
       <c r="E37">
-        <v>-123.97</v>
+        <v>-117.892</v>
       </c>
       <c r="F37">
-        <v>212.73</v>
+        <v>218.808</v>
       </c>
       <c r="G37">
         <v>4.91</v>
@@ -4315,28 +4315,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M37">
-        <v>12.295794</v>
+        <v>12.6471024</v>
       </c>
       <c r="N37">
-        <v>39.07087266666667</v>
+        <v>38.71956426666667</v>
       </c>
       <c r="O37">
-        <v>7.814174533333335</v>
+        <v>7.743912853333335</v>
       </c>
       <c r="P37">
-        <v>31.25669813333334</v>
+        <v>30.97565141333334</v>
       </c>
       <c r="Q37">
-        <v>48.05669813333333</v>
+        <v>47.77565141333334</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08554599200825411</v>
+        <v>0.0860802123309457</v>
       </c>
       <c r="T37">
-        <v>0.7747233634168941</v>
+        <v>0.7851363118499169</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.177580290192457</v>
+        <v>4.061536393242666</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07173773589180525</v>
+        <v>0.07272257697824533</v>
       </c>
       <c r="C38">
-        <v>365.2742219130392</v>
+        <v>338.0098176276822</v>
       </c>
       <c r="D38">
-        <v>579.1722219130393</v>
+        <v>557.9858176276822</v>
       </c>
       <c r="E38">
-        <v>-117.892</v>
+        <v>-111.814</v>
       </c>
       <c r="F38">
-        <v>218.808</v>
+        <v>224.886</v>
       </c>
       <c r="G38">
         <v>4.91</v>
@@ -4397,45 +4397,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M38">
-        <v>12.6471024</v>
+        <v>13.7855118</v>
       </c>
       <c r="N38">
-        <v>38.71956426666667</v>
+        <v>37.58115486666668</v>
       </c>
       <c r="O38">
-        <v>7.743912853333335</v>
+        <v>7.516230973333336</v>
       </c>
       <c r="P38">
-        <v>30.97565141333334</v>
+        <v>30.06492389333334</v>
       </c>
       <c r="Q38">
-        <v>47.77565141333334</v>
+        <v>46.86492389333334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0860802123309457</v>
+        <v>0.08663139202896084</v>
       </c>
       <c r="T38">
-        <v>0.7851363118499168</v>
+        <v>0.7958798300744643</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.061536393242667</v>
+        <v>3.726134177090668</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07272257697824533</v>
+        <v>0.0726994180646854</v>
       </c>
       <c r="C39">
-        <v>338.0098176276822</v>
+        <v>332.4122126045191</v>
       </c>
       <c r="D39">
-        <v>557.9858176276822</v>
+        <v>558.4662126045191</v>
       </c>
       <c r="E39">
-        <v>-111.814</v>
+        <v>-105.736</v>
       </c>
       <c r="F39">
-        <v>224.886</v>
+        <v>230.964</v>
       </c>
       <c r="G39">
         <v>4.91</v>
@@ -4479,28 +4479,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M39">
-        <v>13.7855118</v>
+        <v>14.1580932</v>
       </c>
       <c r="N39">
-        <v>37.58115486666668</v>
+        <v>37.20857346666668</v>
       </c>
       <c r="O39">
-        <v>7.516230973333336</v>
+        <v>7.441714693333336</v>
       </c>
       <c r="P39">
-        <v>30.06492389333334</v>
+        <v>29.76685877333334</v>
       </c>
       <c r="Q39">
-        <v>46.86492389333334</v>
+        <v>46.56685877333334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08663139202896084</v>
+        <v>0.08720035171723452</v>
       </c>
       <c r="T39">
-        <v>0.7958798300744643</v>
+        <v>0.8069699134030291</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.726134177090668</v>
+        <v>3.628078014535649</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0726994180646854</v>
+        <v>0.07267625915112547</v>
       </c>
       <c r="C40">
-        <v>332.4122126045191</v>
+        <v>326.8154354812268</v>
       </c>
       <c r="D40">
-        <v>558.4662126045191</v>
+        <v>558.9474354812269</v>
       </c>
       <c r="E40">
-        <v>-105.736</v>
+        <v>-99.65799999999999</v>
       </c>
       <c r="F40">
-        <v>230.964</v>
+        <v>237.042</v>
       </c>
       <c r="G40">
         <v>4.91</v>
@@ -4561,28 +4561,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M40">
-        <v>14.1580932</v>
+        <v>14.5306746</v>
       </c>
       <c r="N40">
-        <v>37.20857346666668</v>
+        <v>36.83599206666668</v>
       </c>
       <c r="O40">
-        <v>7.441714693333336</v>
+        <v>7.367198413333336</v>
       </c>
       <c r="P40">
-        <v>29.76685877333334</v>
+        <v>29.46879365333334</v>
       </c>
       <c r="Q40">
-        <v>46.56685877333334</v>
+        <v>46.26879365333334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08720035171723452</v>
+        <v>0.08778796582151717</v>
       </c>
       <c r="T40">
-        <v>0.8069699134030291</v>
+        <v>0.8184236060210552</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.628078014535649</v>
+        <v>3.535050373137299</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07267625915112547</v>
+        <v>0.07354910023756556</v>
       </c>
       <c r="C41">
-        <v>326.8154354812268</v>
+        <v>303.1558821093494</v>
       </c>
       <c r="D41">
-        <v>558.9474354812269</v>
+        <v>541.3658821093494</v>
       </c>
       <c r="E41">
-        <v>-99.65799999999999</v>
+        <v>-93.57999999999998</v>
       </c>
       <c r="F41">
-        <v>237.042</v>
+        <v>243.12</v>
       </c>
       <c r="G41">
         <v>4.91</v>
@@ -4643,45 +4643,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M41">
-        <v>14.5306746</v>
+        <v>15.583992</v>
       </c>
       <c r="N41">
-        <v>36.83599206666668</v>
+        <v>35.78267466666667</v>
       </c>
       <c r="O41">
-        <v>7.367198413333336</v>
+        <v>7.156534933333335</v>
       </c>
       <c r="P41">
-        <v>29.46879365333334</v>
+        <v>28.62613973333334</v>
       </c>
       <c r="Q41">
-        <v>46.26879365333334</v>
+        <v>45.42613973333334</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08778796582151717</v>
+        <v>0.08839516706260925</v>
       </c>
       <c r="T41">
-        <v>0.8184236060210552</v>
+        <v>0.8302590883930157</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.535050373137299</v>
+        <v>3.296117366247792</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07354910023756556</v>
+        <v>0.07354834132400562</v>
       </c>
       <c r="C42">
-        <v>303.1558821093494</v>
+        <v>297.0926883964721</v>
       </c>
       <c r="D42">
-        <v>541.3658821093494</v>
+        <v>541.3806883964721</v>
       </c>
       <c r="E42">
-        <v>-93.57999999999998</v>
+        <v>-87.50199999999998</v>
       </c>
       <c r="F42">
-        <v>243.12</v>
+        <v>249.198</v>
       </c>
       <c r="G42">
         <v>4.91</v>
@@ -4725,28 +4725,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M42">
-        <v>15.583992</v>
+        <v>15.9735918</v>
       </c>
       <c r="N42">
-        <v>35.78267466666667</v>
+        <v>35.39307486666667</v>
       </c>
       <c r="O42">
-        <v>7.156534933333335</v>
+        <v>7.078614973333335</v>
       </c>
       <c r="P42">
-        <v>28.62613973333334</v>
+        <v>28.31445989333334</v>
       </c>
       <c r="Q42">
-        <v>45.42613973333334</v>
+        <v>45.11445989333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08839516706260925</v>
+        <v>0.0890229513966197</v>
       </c>
       <c r="T42">
-        <v>0.8302590883930157</v>
+        <v>0.8424957735572458</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.296117366247792</v>
+        <v>3.215724259753944</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07354834132400562</v>
+        <v>0.07354758241044571</v>
       </c>
       <c r="C43">
-        <v>297.0926883964721</v>
+        <v>291.0294954935164</v>
       </c>
       <c r="D43">
-        <v>541.3806883964721</v>
+        <v>541.3954954935165</v>
       </c>
       <c r="E43">
-        <v>-87.50199999999998</v>
+        <v>-81.42399999999998</v>
       </c>
       <c r="F43">
-        <v>249.198</v>
+        <v>255.276</v>
       </c>
       <c r="G43">
         <v>4.91</v>
@@ -4807,28 +4807,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M43">
-        <v>15.9735918</v>
+        <v>16.3631916</v>
       </c>
       <c r="N43">
-        <v>35.39307486666667</v>
+        <v>35.00347506666667</v>
       </c>
       <c r="O43">
-        <v>7.078614973333335</v>
+        <v>7.000695013333335</v>
       </c>
       <c r="P43">
-        <v>28.31445989333334</v>
+        <v>28.00278005333334</v>
       </c>
       <c r="Q43">
-        <v>45.11445989333333</v>
+        <v>44.80278005333334</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.0890229513966197</v>
+        <v>0.0896723834662857</v>
       </c>
       <c r="T43">
-        <v>0.8424957735572458</v>
+        <v>0.8551544133823115</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.215724259753944</v>
+        <v>3.139159396426469</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07354758241044571</v>
+        <v>0.07354682349688578</v>
       </c>
       <c r="C44">
-        <v>291.0294954935165</v>
+        <v>284.9663034005499</v>
       </c>
       <c r="D44">
-        <v>541.3954954935165</v>
+        <v>541.4103034005499</v>
       </c>
       <c r="E44">
-        <v>-81.42400000000001</v>
+        <v>-75.346</v>
       </c>
       <c r="F44">
-        <v>255.276</v>
+        <v>261.354</v>
       </c>
       <c r="G44">
         <v>4.91</v>
@@ -4889,28 +4889,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M44">
-        <v>16.3631916</v>
+        <v>16.7527914</v>
       </c>
       <c r="N44">
-        <v>35.00347506666667</v>
+        <v>34.61387526666667</v>
       </c>
       <c r="O44">
-        <v>7.000695013333335</v>
+        <v>6.922775053333336</v>
       </c>
       <c r="P44">
-        <v>28.00278005333334</v>
+        <v>27.69110021333334</v>
       </c>
       <c r="Q44">
-        <v>44.80278005333334</v>
+        <v>44.49110021333334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08967238346628569</v>
+        <v>0.09034460262611539</v>
       </c>
       <c r="T44">
-        <v>0.8551544133823112</v>
+        <v>0.8682572160082566</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.139159396426469</v>
+        <v>3.066155689532831</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07354682349688578</v>
+        <v>0.07629166458332585</v>
       </c>
       <c r="C45">
-        <v>284.9663034005499</v>
+        <v>230.1508774284542</v>
       </c>
       <c r="D45">
-        <v>541.4103034005499</v>
+        <v>492.6728774284541</v>
       </c>
       <c r="E45">
-        <v>-75.346</v>
+        <v>-69.26800000000003</v>
       </c>
       <c r="F45">
-        <v>261.354</v>
+        <v>267.432</v>
       </c>
       <c r="G45">
         <v>4.91</v>
@@ -4971,45 +4971,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M45">
-        <v>16.7527914</v>
+        <v>19.2283608</v>
       </c>
       <c r="N45">
-        <v>34.61387526666667</v>
+        <v>32.13830586666668</v>
       </c>
       <c r="O45">
-        <v>6.922775053333336</v>
+        <v>6.427661173333336</v>
       </c>
       <c r="P45">
-        <v>27.69110021333334</v>
+        <v>25.71064469333334</v>
       </c>
       <c r="Q45">
-        <v>44.49110021333334</v>
+        <v>42.51064469333334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09034460262611539</v>
+        <v>0.09104082961308188</v>
       </c>
       <c r="T45">
-        <v>0.8682572160082566</v>
+        <v>0.8818279758708426</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.066155689532831</v>
+        <v>2.671401228682305</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07629166458332585</v>
+        <v>0.07635330566976593</v>
       </c>
       <c r="C46">
-        <v>230.1508774284542</v>
+        <v>223.0789132481952</v>
       </c>
       <c r="D46">
-        <v>492.6728774284541</v>
+        <v>491.6789132481952</v>
       </c>
       <c r="E46">
-        <v>-69.26800000000003</v>
+        <v>-63.19</v>
       </c>
       <c r="F46">
-        <v>267.432</v>
+        <v>273.51</v>
       </c>
       <c r="G46">
         <v>4.91</v>
@@ -5053,28 +5053,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M46">
-        <v>19.2283608</v>
+        <v>19.665369</v>
       </c>
       <c r="N46">
-        <v>32.13830586666668</v>
+        <v>31.70129766666667</v>
       </c>
       <c r="O46">
-        <v>6.427661173333336</v>
+        <v>6.340259533333334</v>
       </c>
       <c r="P46">
-        <v>25.71064469333334</v>
+        <v>25.36103813333334</v>
       </c>
       <c r="Q46">
-        <v>42.51064469333334</v>
+        <v>42.16103813333334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09104082961308188</v>
+        <v>0.09176237394502895</v>
       </c>
       <c r="T46">
-        <v>0.8818279758708426</v>
+        <v>0.89589221791025</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.671401228682305</v>
+        <v>2.61203675693381</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07635330566976593</v>
+        <v>0.07641494675620601</v>
       </c>
       <c r="C47">
-        <v>223.0789132481952</v>
+        <v>216.0109516247555</v>
       </c>
       <c r="D47">
-        <v>491.6789132481952</v>
+        <v>490.6889516247555</v>
       </c>
       <c r="E47">
-        <v>-63.19</v>
+        <v>-57.11200000000002</v>
       </c>
       <c r="F47">
-        <v>273.51</v>
+        <v>279.588</v>
       </c>
       <c r="G47">
         <v>4.91</v>
@@ -5135,28 +5135,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M47">
-        <v>19.665369</v>
+        <v>20.1023772</v>
       </c>
       <c r="N47">
-        <v>31.70129766666667</v>
+        <v>31.26428946666667</v>
       </c>
       <c r="O47">
-        <v>6.340259533333334</v>
+        <v>6.252857893333335</v>
       </c>
       <c r="P47">
-        <v>25.36103813333334</v>
+        <v>25.01143157333334</v>
       </c>
       <c r="Q47">
-        <v>42.16103813333334</v>
+        <v>41.81143157333334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09176237394502895</v>
+        <v>0.09251064214112223</v>
       </c>
       <c r="T47">
-        <v>0.89589221791025</v>
+        <v>0.9104773578029688</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.61203675693381</v>
+        <v>2.555253349174379</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07641494675620601</v>
+        <v>0.07647658784264608</v>
       </c>
       <c r="C48">
-        <v>216.0109516247555</v>
+        <v>208.9469684300979</v>
       </c>
       <c r="D48">
-        <v>490.6889516247555</v>
+        <v>489.7029684300978</v>
       </c>
       <c r="E48">
-        <v>-57.11200000000002</v>
+        <v>-51.03399999999999</v>
       </c>
       <c r="F48">
-        <v>279.588</v>
+        <v>285.666</v>
       </c>
       <c r="G48">
         <v>4.91</v>
@@ -5217,28 +5217,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M48">
-        <v>20.1023772</v>
+        <v>20.5393854</v>
       </c>
       <c r="N48">
-        <v>31.26428946666667</v>
+        <v>30.82728126666667</v>
       </c>
       <c r="O48">
-        <v>6.252857893333335</v>
+        <v>6.165456253333335</v>
       </c>
       <c r="P48">
-        <v>25.01143157333334</v>
+        <v>24.66182501333334</v>
       </c>
       <c r="Q48">
-        <v>41.81143157333334</v>
+        <v>41.46182501333334</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09251064214112223</v>
+        <v>0.09328714687291711</v>
       </c>
       <c r="T48">
-        <v>0.9104773578029688</v>
+        <v>0.9256128803331486</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.555253349174379</v>
+        <v>2.500886256638754</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07647658784264608</v>
+        <v>0.07803582892908616</v>
       </c>
       <c r="C49">
-        <v>208.9469684300979</v>
+        <v>179.1821263697431</v>
       </c>
       <c r="D49">
-        <v>489.7029684300978</v>
+        <v>466.0161263697431</v>
       </c>
       <c r="E49">
-        <v>-51.03399999999999</v>
+        <v>-44.95599999999996</v>
       </c>
       <c r="F49">
-        <v>285.666</v>
+        <v>291.744</v>
       </c>
       <c r="G49">
         <v>4.91</v>
@@ -5299,45 +5299,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M49">
-        <v>20.5393854</v>
+        <v>22.1141952</v>
       </c>
       <c r="N49">
-        <v>30.82728126666667</v>
+        <v>29.25247146666667</v>
       </c>
       <c r="O49">
-        <v>6.165456253333335</v>
+        <v>5.850494293333334</v>
       </c>
       <c r="P49">
-        <v>24.66182501333334</v>
+        <v>23.40197717333334</v>
       </c>
       <c r="Q49">
-        <v>41.46182501333334</v>
+        <v>40.20197717333333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09328714687291711</v>
+        <v>0.09409351717131952</v>
       </c>
       <c r="T49">
-        <v>0.9256128803331486</v>
+        <v>0.9413305383452585</v>
       </c>
       <c r="U49">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.500886256638754</v>
+        <v>2.322791591649994</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07803582892908616</v>
+        <v>0.07812867001552623</v>
       </c>
       <c r="C50">
-        <v>179.1821263697431</v>
+        <v>171.7658268526278</v>
       </c>
       <c r="D50">
-        <v>466.0161263697431</v>
+        <v>464.6778268526277</v>
       </c>
       <c r="E50">
-        <v>-44.95600000000002</v>
+        <v>-38.87800000000004</v>
       </c>
       <c r="F50">
-        <v>291.744</v>
+        <v>297.8219999999999</v>
       </c>
       <c r="G50">
         <v>4.91</v>
@@ -5381,28 +5381,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M50">
-        <v>22.1141952</v>
+        <v>22.5749076</v>
       </c>
       <c r="N50">
-        <v>29.25247146666667</v>
+        <v>28.79175906666667</v>
       </c>
       <c r="O50">
-        <v>5.850494293333335</v>
+        <v>5.758351813333335</v>
       </c>
       <c r="P50">
-        <v>23.40197717333334</v>
+        <v>23.03340725333334</v>
       </c>
       <c r="Q50">
-        <v>40.20197717333333</v>
+        <v>39.83340725333333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09409351717131952</v>
+        <v>0.09493150983436514</v>
       </c>
       <c r="T50">
-        <v>0.9413305383452585</v>
+        <v>0.9576645751029412</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.322791591649994</v>
+        <v>2.275387681616321</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07812867001552623</v>
+        <v>0.0782215111019663</v>
       </c>
       <c r="C51">
-        <v>171.7658268526278</v>
+        <v>164.3571919493399</v>
       </c>
       <c r="D51">
-        <v>464.6778268526277</v>
+        <v>463.3471919493399</v>
       </c>
       <c r="E51">
-        <v>-38.87800000000004</v>
+        <v>-32.80000000000001</v>
       </c>
       <c r="F51">
-        <v>297.8219999999999</v>
+        <v>303.9</v>
       </c>
       <c r="G51">
         <v>4.91</v>
@@ -5463,28 +5463,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M51">
-        <v>22.5749076</v>
+        <v>23.03562</v>
       </c>
       <c r="N51">
-        <v>28.79175906666667</v>
+        <v>28.33104666666667</v>
       </c>
       <c r="O51">
-        <v>5.758351813333335</v>
+        <v>5.666209333333335</v>
       </c>
       <c r="P51">
-        <v>23.03340725333334</v>
+        <v>22.66483733333334</v>
       </c>
       <c r="Q51">
-        <v>39.83340725333333</v>
+        <v>39.46483733333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09493150983436514</v>
+        <v>0.09580302220393261</v>
       </c>
       <c r="T51">
-        <v>0.9576645751029412</v>
+        <v>0.9746519733309313</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.275387681616321</v>
+        <v>2.229879927983995</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0782215111019663</v>
+        <v>0.07831435218840638</v>
       </c>
       <c r="C52">
-        <v>164.3571919493399</v>
+        <v>156.9561560035439</v>
       </c>
       <c r="D52">
-        <v>463.3471919493399</v>
+        <v>462.0241560035439</v>
       </c>
       <c r="E52">
-        <v>-32.80000000000001</v>
+        <v>-26.72199999999998</v>
       </c>
       <c r="F52">
-        <v>303.9</v>
+        <v>309.978</v>
       </c>
       <c r="G52">
         <v>4.91</v>
@@ -5545,28 +5545,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M52">
-        <v>23.03562</v>
+        <v>23.4963324</v>
       </c>
       <c r="N52">
-        <v>28.33104666666667</v>
+        <v>27.87033426666667</v>
       </c>
       <c r="O52">
-        <v>5.666209333333335</v>
+        <v>5.574066853333335</v>
       </c>
       <c r="P52">
-        <v>22.66483733333334</v>
+        <v>22.29626741333334</v>
       </c>
       <c r="Q52">
-        <v>39.46483733333334</v>
+        <v>39.09626741333334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09580302220393261</v>
+        <v>0.09671010650695178</v>
       </c>
       <c r="T52">
-        <v>0.9746519733309313</v>
+        <v>0.9923327347519006</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.229879927983995</v>
+        <v>2.186156792141171</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07831435218840638</v>
+        <v>0.07840719327484645</v>
       </c>
       <c r="C53">
-        <v>156.9561560035439</v>
+        <v>149.5626541066659</v>
       </c>
       <c r="D53">
-        <v>462.0241560035439</v>
+        <v>460.7086541066658</v>
       </c>
       <c r="E53">
-        <v>-26.72199999999998</v>
+        <v>-20.64400000000001</v>
       </c>
       <c r="F53">
-        <v>309.978</v>
+        <v>316.056</v>
       </c>
       <c r="G53">
         <v>4.91</v>
@@ -5627,28 +5627,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M53">
-        <v>23.4963324</v>
+        <v>23.9570448</v>
       </c>
       <c r="N53">
-        <v>27.87033426666667</v>
+        <v>27.40962186666667</v>
       </c>
       <c r="O53">
-        <v>5.574066853333335</v>
+        <v>5.481924373333335</v>
       </c>
       <c r="P53">
-        <v>22.29626741333334</v>
+        <v>21.92769749333334</v>
       </c>
       <c r="Q53">
-        <v>39.09626741333334</v>
+        <v>38.72769749333334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09671010650695178</v>
+        <v>0.09765498598926343</v>
       </c>
       <c r="T53">
-        <v>0.9923327347519006</v>
+        <v>1.01075019456541</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.186156792141171</v>
+        <v>2.144115315369226</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07840719327484645</v>
+        <v>0.07850003436128652</v>
       </c>
       <c r="C54">
-        <v>149.5626541066659</v>
+        <v>142.1766220872792</v>
       </c>
       <c r="D54">
-        <v>460.7086541066658</v>
+        <v>459.4006220872792</v>
       </c>
       <c r="E54">
-        <v>-20.64400000000001</v>
+        <v>-14.56599999999997</v>
       </c>
       <c r="F54">
-        <v>316.056</v>
+        <v>322.134</v>
       </c>
       <c r="G54">
         <v>4.91</v>
@@ -5709,28 +5709,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M54">
-        <v>23.9570448</v>
+        <v>24.4177572</v>
       </c>
       <c r="N54">
-        <v>27.40962186666667</v>
+        <v>26.94890946666667</v>
       </c>
       <c r="O54">
-        <v>5.481924373333335</v>
+        <v>5.389781893333335</v>
       </c>
       <c r="P54">
-        <v>21.92769749333334</v>
+        <v>21.55912757333333</v>
       </c>
       <c r="Q54">
-        <v>38.72769749333334</v>
+        <v>38.35912757333333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09765498598926343</v>
+        <v>0.09864007310912026</v>
       </c>
       <c r="T54">
-        <v>1.01075019456541</v>
+        <v>1.029951376073112</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.144115315369226</v>
+        <v>2.103660309418863</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07850003436128652</v>
+        <v>0.07859287544772661</v>
       </c>
       <c r="C55">
-        <v>142.1766220872792</v>
+        <v>134.7979965006691</v>
       </c>
       <c r="D55">
-        <v>459.4006220872792</v>
+        <v>458.099996500669</v>
       </c>
       <c r="E55">
-        <v>-14.56599999999997</v>
+        <v>-8.488</v>
       </c>
       <c r="F55">
-        <v>322.134</v>
+        <v>328.212</v>
       </c>
       <c r="G55">
         <v>4.91</v>
@@ -5791,28 +5791,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M55">
-        <v>24.4177572</v>
+        <v>24.8784696</v>
       </c>
       <c r="N55">
-        <v>26.94890946666667</v>
+        <v>26.48819706666667</v>
       </c>
       <c r="O55">
-        <v>5.389781893333335</v>
+        <v>5.297639413333335</v>
       </c>
       <c r="P55">
-        <v>21.55912757333333</v>
+        <v>21.19055765333334</v>
       </c>
       <c r="Q55">
-        <v>38.35912757333333</v>
+        <v>37.99055765333333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09864007310912026</v>
+        <v>0.09966799010375348</v>
       </c>
       <c r="T55">
-        <v>1.029951376073112</v>
+        <v>1.049987391559409</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.103660309418863</v>
+        <v>2.064703637022217</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07859287544772661</v>
+        <v>0.07868571653416667</v>
       </c>
       <c r="C56">
-        <v>134.7979965006691</v>
+        <v>127.4267146185752</v>
       </c>
       <c r="D56">
-        <v>458.099996500669</v>
+        <v>456.8067146185752</v>
       </c>
       <c r="E56">
-        <v>-8.488</v>
+        <v>-2.409999999999968</v>
       </c>
       <c r="F56">
-        <v>328.212</v>
+        <v>334.29</v>
       </c>
       <c r="G56">
         <v>4.91</v>
@@ -5873,28 +5873,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M56">
-        <v>24.8784696</v>
+        <v>25.339182</v>
       </c>
       <c r="N56">
-        <v>26.48819706666667</v>
+        <v>26.02748466666667</v>
       </c>
       <c r="O56">
-        <v>5.297639413333335</v>
+        <v>5.205496933333334</v>
       </c>
       <c r="P56">
-        <v>21.19055765333334</v>
+        <v>20.82198773333334</v>
       </c>
       <c r="Q56">
-        <v>37.99055765333333</v>
+        <v>37.62198773333333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09966799010375348</v>
+        <v>0.1007415922981482</v>
       </c>
       <c r="T56">
-        <v>1.049987391559409</v>
+        <v>1.070913896622875</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.064703637022217</v>
+        <v>2.02716357089454</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07868571653416667</v>
+        <v>0.08514015762060675</v>
       </c>
       <c r="C57">
-        <v>127.4267146185752</v>
+        <v>46.40158156867039</v>
       </c>
       <c r="D57">
-        <v>456.8067146185752</v>
+        <v>381.8595815686704</v>
       </c>
       <c r="E57">
-        <v>-2.409999999999968</v>
+        <v>3.668000000000006</v>
       </c>
       <c r="F57">
-        <v>334.29</v>
+        <v>340.368</v>
       </c>
       <c r="G57">
         <v>4.91</v>
@@ -5955,45 +5955,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M57">
-        <v>25.339182</v>
+        <v>30.63312</v>
       </c>
       <c r="N57">
-        <v>26.02748466666667</v>
+        <v>20.73354666666668</v>
       </c>
       <c r="O57">
-        <v>5.205496933333334</v>
+        <v>4.146709333333336</v>
       </c>
       <c r="P57">
-        <v>20.82198773333334</v>
+        <v>16.58683733333334</v>
       </c>
       <c r="Q57">
-        <v>37.62198773333333</v>
+        <v>33.38683733333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1007415922981482</v>
+        <v>0.1018639945922881</v>
       </c>
       <c r="T57">
-        <v>1.070913896622875</v>
+        <v>1.092791606461953</v>
       </c>
       <c r="U57">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V57">
         <v>0.2</v>
       </c>
       <c r="W57">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.02716357089454</v>
+        <v>1.676834310924473</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08514015762060675</v>
+        <v>0.08534659870704682</v>
       </c>
       <c r="C58">
-        <v>46.40158156867039</v>
+        <v>38.33019883882929</v>
       </c>
       <c r="D58">
-        <v>381.8595815686704</v>
+        <v>379.8661988388293</v>
       </c>
       <c r="E58">
-        <v>3.668000000000006</v>
+        <v>9.746000000000038</v>
       </c>
       <c r="F58">
-        <v>340.368</v>
+        <v>346.446</v>
       </c>
       <c r="G58">
         <v>4.91</v>
@@ -6037,28 +6037,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M58">
-        <v>30.63312</v>
+        <v>31.18014</v>
       </c>
       <c r="N58">
-        <v>20.73354666666668</v>
+        <v>20.18652666666667</v>
       </c>
       <c r="O58">
-        <v>4.146709333333336</v>
+        <v>4.037305333333335</v>
       </c>
       <c r="P58">
-        <v>16.58683733333334</v>
+        <v>16.14922133333334</v>
       </c>
       <c r="Q58">
-        <v>33.38683733333334</v>
+        <v>32.94922133333333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1018639945922881</v>
+        <v>0.1030386016442949</v>
       </c>
       <c r="T58">
-        <v>1.092791606461953</v>
+        <v>1.115686884200524</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.676834310924473</v>
+        <v>1.64741616511878</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08534659870704682</v>
+        <v>0.0855530397934869</v>
       </c>
       <c r="C59">
-        <v>38.33019883882929</v>
+        <v>30.2795197381231</v>
       </c>
       <c r="D59">
-        <v>379.8661988388293</v>
+        <v>377.8935197381231</v>
       </c>
       <c r="E59">
-        <v>9.746000000000038</v>
+        <v>15.82400000000001</v>
       </c>
       <c r="F59">
-        <v>346.446</v>
+        <v>352.524</v>
       </c>
       <c r="G59">
         <v>4.91</v>
@@ -6119,28 +6119,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M59">
-        <v>31.18014</v>
+        <v>31.72716</v>
       </c>
       <c r="N59">
-        <v>20.18652666666667</v>
+        <v>19.63950666666668</v>
       </c>
       <c r="O59">
-        <v>4.037305333333335</v>
+        <v>3.927901333333335</v>
       </c>
       <c r="P59">
-        <v>16.14922133333334</v>
+        <v>15.71160533333334</v>
       </c>
       <c r="Q59">
-        <v>32.94922133333333</v>
+        <v>32.51160533333334</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1030386016442949</v>
+        <v>0.104269142365445</v>
       </c>
       <c r="T59">
-        <v>1.115686884200524</v>
+        <v>1.139672413259978</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.64741616511878</v>
+        <v>1.619012438133973</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08555303979348688</v>
+        <v>0.08575948087992696</v>
       </c>
       <c r="C60">
-        <v>30.27951973812333</v>
+        <v>22.24922338553</v>
       </c>
       <c r="D60">
-        <v>377.8935197381232</v>
+        <v>375.94122338553</v>
       </c>
       <c r="E60">
-        <v>15.82399999999996</v>
+        <v>21.90199999999999</v>
       </c>
       <c r="F60">
-        <v>352.5239999999999</v>
+        <v>358.602</v>
       </c>
       <c r="G60">
         <v>4.91</v>
@@ -6201,28 +6201,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M60">
-        <v>31.72715999999999</v>
+        <v>32.27417999999999</v>
       </c>
       <c r="N60">
-        <v>19.63950666666668</v>
+        <v>19.09248666666668</v>
       </c>
       <c r="O60">
-        <v>3.927901333333336</v>
+        <v>3.818497333333336</v>
       </c>
       <c r="P60">
-        <v>15.71160533333334</v>
+        <v>15.27398933333334</v>
       </c>
       <c r="Q60">
-        <v>32.51160533333334</v>
+        <v>32.07398933333334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.104269142365445</v>
+        <v>0.1055597094632365</v>
       </c>
       <c r="T60">
-        <v>1.139672413259978</v>
+        <v>1.164827968127211</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.619012438133974</v>
+        <v>1.591571549352042</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08575948087992696</v>
+        <v>0.08596592196636704</v>
       </c>
       <c r="C61">
-        <v>22.24922338553</v>
+        <v>14.23899549696546</v>
       </c>
       <c r="D61">
-        <v>375.94122338553</v>
+        <v>374.0089954969654</v>
       </c>
       <c r="E61">
-        <v>21.90199999999999</v>
+        <v>27.97999999999996</v>
       </c>
       <c r="F61">
-        <v>358.602</v>
+        <v>364.6799999999999</v>
       </c>
       <c r="G61">
         <v>4.91</v>
@@ -6283,28 +6283,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M61">
-        <v>32.27417999999999</v>
+        <v>32.8212</v>
       </c>
       <c r="N61">
-        <v>19.09248666666668</v>
+        <v>18.54546666666668</v>
       </c>
       <c r="O61">
-        <v>3.818497333333336</v>
+        <v>3.709093333333335</v>
       </c>
       <c r="P61">
-        <v>15.27398933333334</v>
+        <v>14.83637333333334</v>
       </c>
       <c r="Q61">
-        <v>32.07398933333334</v>
+        <v>31.63637333333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1055597094632365</v>
+        <v>0.1069148049159176</v>
       </c>
       <c r="T61">
-        <v>1.164827968127211</v>
+        <v>1.191241300737805</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.591571549352042</v>
+        <v>1.565045356862841</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08596592196636704</v>
+        <v>0.08617236305280712</v>
       </c>
       <c r="C62">
-        <v>14.23899549696546</v>
+        <v>6.24852821661915</v>
       </c>
       <c r="D62">
-        <v>374.0089954969654</v>
+        <v>372.0965282166191</v>
       </c>
       <c r="E62">
-        <v>27.97999999999996</v>
+        <v>34.05799999999999</v>
       </c>
       <c r="F62">
-        <v>364.6799999999999</v>
+        <v>370.758</v>
       </c>
       <c r="G62">
         <v>4.91</v>
@@ -6365,28 +6365,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M62">
-        <v>32.8212</v>
+        <v>33.36821999999999</v>
       </c>
       <c r="N62">
-        <v>18.54546666666668</v>
+        <v>17.99844666666668</v>
       </c>
       <c r="O62">
-        <v>3.709093333333335</v>
+        <v>3.599689333333336</v>
       </c>
       <c r="P62">
-        <v>14.83637333333334</v>
+        <v>14.39875733333334</v>
       </c>
       <c r="Q62">
-        <v>31.63637333333334</v>
+        <v>31.19875733333334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1069148049159176</v>
+        <v>0.1083393924430952</v>
       </c>
       <c r="T62">
-        <v>1.191241300737805</v>
+        <v>1.219009163225866</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.565045356862841</v>
+        <v>1.539388875602794</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08617236305280712</v>
+        <v>0.0863788041392472</v>
       </c>
       <c r="C63">
-        <v>6.24852821661915</v>
+        <v>-1.722480046562339</v>
       </c>
       <c r="D63">
-        <v>372.0965282166191</v>
+        <v>370.2035199534376</v>
       </c>
       <c r="E63">
-        <v>34.05799999999999</v>
+        <v>40.13599999999997</v>
       </c>
       <c r="F63">
-        <v>370.758</v>
+        <v>376.836</v>
       </c>
       <c r="G63">
         <v>4.91</v>
@@ -6447,28 +6447,28 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M63">
-        <v>33.36821999999999</v>
+        <v>33.91524</v>
       </c>
       <c r="N63">
-        <v>17.99844666666668</v>
+        <v>17.45142666666668</v>
       </c>
       <c r="O63">
-        <v>3.599689333333336</v>
+        <v>3.490285333333336</v>
       </c>
       <c r="P63">
-        <v>14.39875733333334</v>
+        <v>13.96114133333334</v>
       </c>
       <c r="Q63">
-        <v>31.19875733333334</v>
+        <v>30.76114133333334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1083393924430952</v>
+        <v>0.1098389582611768</v>
       </c>
       <c r="T63">
-        <v>1.219009163225866</v>
+        <v>1.248238492160666</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.539388875602794</v>
+        <v>1.514560022770491</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0863788041392472</v>
+        <v>0.1171084520322727</v>
       </c>
       <c r="C64">
-        <v>-1.722480046562339</v>
+        <v>-167.335899659642</v>
       </c>
       <c r="D64">
-        <v>370.2035199534376</v>
+        <v>210.668100340358</v>
       </c>
       <c r="E64">
-        <v>40.13599999999997</v>
+        <v>46.214</v>
       </c>
       <c r="F64">
-        <v>376.836</v>
+        <v>382.914</v>
       </c>
       <c r="G64">
         <v>4.91</v>
@@ -6529,45 +6529,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M64">
-        <v>33.91524</v>
+        <v>56.21177520000001</v>
       </c>
       <c r="N64">
-        <v>17.45142666666668</v>
+        <v>-4.845108533333331</v>
       </c>
       <c r="O64">
-        <v>3.490285333333336</v>
+        <v>-0.9690217066666662</v>
       </c>
       <c r="P64">
-        <v>13.96114133333334</v>
+        <v>-3.876086826666665</v>
       </c>
       <c r="Q64">
-        <v>30.76114133333334</v>
+        <v>12.92391317333333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1098389582611768</v>
+        <v>0.1122349780713281</v>
       </c>
       <c r="T64">
-        <v>1.248238492160666</v>
+        <v>1.294941377969842</v>
       </c>
       <c r="U64">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2</v>
+        <v>0.1827612327983076</v>
       </c>
       <c r="W64">
-        <v>0.07199999999999999</v>
+        <v>0.1199706510252085</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.514560022770491</v>
+        <v>0.913806163991538</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1171084520322727</v>
+        <v>0.1181184520322727</v>
       </c>
       <c r="C65">
-        <v>-167.335899659642</v>
+        <v>-176.3560918023721</v>
       </c>
       <c r="D65">
-        <v>210.668100340358</v>
+        <v>207.7259081976278</v>
       </c>
       <c r="E65">
-        <v>46.214</v>
+        <v>52.29199999999997</v>
       </c>
       <c r="F65">
-        <v>382.914</v>
+        <v>388.992</v>
       </c>
       <c r="G65">
         <v>4.91</v>
@@ -6611,37 +6611,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M65">
-        <v>56.21177520000001</v>
+        <v>57.1040256</v>
       </c>
       <c r="N65">
-        <v>-4.845108533333331</v>
+        <v>-5.737358933333326</v>
       </c>
       <c r="O65">
-        <v>-0.9690217066666662</v>
+        <v>-1.147471786666665</v>
       </c>
       <c r="P65">
-        <v>-3.876086826666665</v>
+        <v>-4.58988714666666</v>
       </c>
       <c r="Q65">
-        <v>12.92391317333333</v>
+        <v>12.21011285333334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1122349780713281</v>
+        <v>0.114080394128865</v>
       </c>
       <c r="T65">
-        <v>1.294941377969842</v>
+        <v>1.330911971802338</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1827612327983076</v>
+        <v>0.1799055885358341</v>
       </c>
       <c r="W65">
-        <v>0.1199706510252085</v>
+        <v>0.1203898596029396</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.913806163991538</v>
+        <v>0.8995279426791704</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1181184520322727</v>
+        <v>0.1191284520322727</v>
       </c>
       <c r="C66">
-        <v>-176.3560918023721</v>
+        <v>-185.2952345302627</v>
       </c>
       <c r="D66">
-        <v>207.7259081976278</v>
+        <v>204.8647654697373</v>
       </c>
       <c r="E66">
-        <v>52.29199999999997</v>
+        <v>58.37</v>
       </c>
       <c r="F66">
-        <v>388.992</v>
+        <v>395.07</v>
       </c>
       <c r="G66">
         <v>4.91</v>
@@ -6693,37 +6693,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M66">
-        <v>57.1040256</v>
+        <v>57.996276</v>
       </c>
       <c r="N66">
-        <v>-5.737358933333326</v>
+        <v>-6.629609333333327</v>
       </c>
       <c r="O66">
-        <v>-1.147471786666665</v>
+        <v>-1.325921866666666</v>
       </c>
       <c r="P66">
-        <v>-4.58988714666666</v>
+        <v>-5.303687466666662</v>
       </c>
       <c r="Q66">
-        <v>12.21011285333334</v>
+        <v>11.49631253333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.114080394128865</v>
+        <v>0.1160312625325469</v>
       </c>
       <c r="T66">
-        <v>1.330911971802338</v>
+        <v>1.368938028139548</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1799055885358341</v>
+        <v>0.1771378102506674</v>
       </c>
       <c r="W66">
-        <v>0.1203898596029396</v>
+        <v>0.1207961694552021</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8995279426791704</v>
+        <v>0.8856890512533369</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1191284520322727</v>
+        <v>0.1201384520322727</v>
       </c>
       <c r="C67">
-        <v>-185.2952345302627</v>
+        <v>-194.1566313789703</v>
       </c>
       <c r="D67">
-        <v>204.8647654697373</v>
+        <v>202.0813686210297</v>
       </c>
       <c r="E67">
-        <v>58.37</v>
+        <v>64.44799999999998</v>
       </c>
       <c r="F67">
-        <v>395.07</v>
+        <v>401.148</v>
       </c>
       <c r="G67">
         <v>4.91</v>
@@ -6775,37 +6775,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M67">
-        <v>57.996276</v>
+        <v>58.8885264</v>
       </c>
       <c r="N67">
-        <v>-6.629609333333327</v>
+        <v>-7.521859733333329</v>
       </c>
       <c r="O67">
-        <v>-1.325921866666666</v>
+        <v>-1.504371946666666</v>
       </c>
       <c r="P67">
-        <v>-5.303687466666662</v>
+        <v>-6.017487786666663</v>
       </c>
       <c r="Q67">
-        <v>11.49631253333333</v>
+        <v>10.78251221333333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1160312625325469</v>
+        <v>0.1180968879011512</v>
       </c>
       <c r="T67">
-        <v>1.368938028139548</v>
+        <v>1.409200911320122</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1771378102506674</v>
+        <v>0.1744539040347482</v>
       </c>
       <c r="W67">
-        <v>0.1207961694552021</v>
+        <v>0.121190166887699</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8856890512533369</v>
+        <v>0.8722695201737408</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1201384520322727</v>
+        <v>0.1211484520322727</v>
       </c>
       <c r="C68">
-        <v>-194.1566313789703</v>
+        <v>-202.9434087566373</v>
       </c>
       <c r="D68">
-        <v>202.0813686210297</v>
+        <v>199.3725912433627</v>
       </c>
       <c r="E68">
-        <v>64.44799999999998</v>
+        <v>70.52600000000001</v>
       </c>
       <c r="F68">
-        <v>401.148</v>
+        <v>407.226</v>
       </c>
       <c r="G68">
         <v>4.91</v>
@@ -6857,37 +6857,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M68">
-        <v>58.8885264</v>
+        <v>59.78077680000001</v>
       </c>
       <c r="N68">
-        <v>-7.521859733333329</v>
+        <v>-8.414110133333331</v>
       </c>
       <c r="O68">
-        <v>-1.504371946666666</v>
+        <v>-1.682822026666666</v>
       </c>
       <c r="P68">
-        <v>-6.017487786666663</v>
+        <v>-6.731288106666665</v>
       </c>
       <c r="Q68">
-        <v>10.78251221333333</v>
+        <v>10.06871189333333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1180968879011512</v>
+        <v>0.1202877026860346</v>
       </c>
       <c r="T68">
-        <v>1.409200911320122</v>
+        <v>1.451903969238914</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1744539040347482</v>
+        <v>0.1718501144222893</v>
       </c>
       <c r="W68">
-        <v>0.121190166887699</v>
+        <v>0.1215724032028079</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8722695201737408</v>
+        <v>0.8592505721114462</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1211484520322727</v>
+        <v>0.1221584520322727</v>
       </c>
       <c r="C69">
-        <v>-202.9434087566373</v>
+        <v>-211.6585276582971</v>
       </c>
       <c r="D69">
-        <v>199.3725912433627</v>
+        <v>196.7354723417028</v>
       </c>
       <c r="E69">
-        <v>70.52600000000001</v>
+        <v>76.60399999999998</v>
       </c>
       <c r="F69">
-        <v>407.226</v>
+        <v>413.304</v>
       </c>
       <c r="G69">
         <v>4.91</v>
@@ -6939,37 +6939,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M69">
-        <v>59.78077680000001</v>
+        <v>60.6730272</v>
       </c>
       <c r="N69">
-        <v>-8.414110133333331</v>
+        <v>-9.306360533333326</v>
       </c>
       <c r="O69">
-        <v>-1.682822026666666</v>
+        <v>-1.861272106666665</v>
       </c>
       <c r="P69">
-        <v>-6.731288106666665</v>
+        <v>-7.44508842666666</v>
       </c>
       <c r="Q69">
-        <v>10.06871189333333</v>
+        <v>9.354911573333336</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1202877026860346</v>
+        <v>0.1226154433949731</v>
       </c>
       <c r="T69">
-        <v>1.451903969238914</v>
+        <v>1.49727596827763</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1718501144222893</v>
+        <v>0.1693229068572556</v>
       </c>
       <c r="W69">
-        <v>0.1215724032028079</v>
+        <v>0.1219433972733549</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8592505721114462</v>
+        <v>0.846614534286278</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1221584520322727</v>
+        <v>0.1231684520322727</v>
       </c>
       <c r="C70">
-        <v>-211.6585276582971</v>
+        <v>-220.3047944627337</v>
       </c>
       <c r="D70">
-        <v>196.7354723417028</v>
+        <v>194.1672055372663</v>
       </c>
       <c r="E70">
-        <v>76.60399999999998</v>
+        <v>82.68200000000002</v>
       </c>
       <c r="F70">
-        <v>413.304</v>
+        <v>419.382</v>
       </c>
       <c r="G70">
         <v>4.91</v>
@@ -7021,37 +7021,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M70">
-        <v>60.6730272</v>
+        <v>61.56527760000001</v>
       </c>
       <c r="N70">
-        <v>-9.306360533333326</v>
+        <v>-10.19861093333333</v>
       </c>
       <c r="O70">
-        <v>-1.861272106666665</v>
+        <v>-2.039722186666667</v>
       </c>
       <c r="P70">
-        <v>-7.44508842666666</v>
+        <v>-8.158888746666667</v>
       </c>
       <c r="Q70">
-        <v>9.354911573333336</v>
+        <v>8.64111125333333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1226154433949731</v>
+        <v>0.1250933609238432</v>
       </c>
       <c r="T70">
-        <v>1.49727596827763</v>
+        <v>1.54557519306078</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1693229068572556</v>
+        <v>0.1668689516854113</v>
       </c>
       <c r="W70">
-        <v>0.1219433972733549</v>
+        <v>0.1223036378925816</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.846614534286278</v>
+        <v>0.8343447584270565</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1231684520322727</v>
+        <v>0.1241784520322727</v>
       </c>
       <c r="C71">
-        <v>-220.3047944627337</v>
+        <v>-228.8848708945557</v>
       </c>
       <c r="D71">
-        <v>194.1672055372663</v>
+        <v>191.6651291054444</v>
       </c>
       <c r="E71">
-        <v>82.68200000000002</v>
+        <v>88.76000000000005</v>
       </c>
       <c r="F71">
-        <v>419.382</v>
+        <v>425.46</v>
       </c>
       <c r="G71">
         <v>4.91</v>
@@ -7103,37 +7103,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M71">
-        <v>61.56527760000001</v>
+        <v>62.45752800000001</v>
       </c>
       <c r="N71">
-        <v>-10.19861093333333</v>
+        <v>-11.09086133333334</v>
       </c>
       <c r="O71">
-        <v>-2.039722186666667</v>
+        <v>-2.218172266666667</v>
       </c>
       <c r="P71">
-        <v>-8.158888746666667</v>
+        <v>-8.87268906666667</v>
       </c>
       <c r="Q71">
-        <v>8.64111125333333</v>
+        <v>7.927310933333327</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1250933609238432</v>
+        <v>0.127736472954638</v>
       </c>
       <c r="T71">
-        <v>1.54557519306078</v>
+        <v>1.597094366162806</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1668689516854113</v>
+        <v>0.1644851095184768</v>
       </c>
       <c r="W71">
-        <v>0.1223036378925816</v>
+        <v>0.1226535859226876</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8343447584270565</v>
+        <v>0.8224255475923842</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1241784520322727</v>
+        <v>0.1251884520322727</v>
       </c>
       <c r="C72">
-        <v>-228.8848708945557</v>
+        <v>-237.4012832258328</v>
       </c>
       <c r="D72">
-        <v>191.6651291054444</v>
+        <v>189.2267167741672</v>
       </c>
       <c r="E72">
-        <v>88.76000000000005</v>
+        <v>94.83800000000002</v>
       </c>
       <c r="F72">
-        <v>425.46</v>
+        <v>431.538</v>
       </c>
       <c r="G72">
         <v>4.91</v>
@@ -7185,37 +7185,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M72">
-        <v>62.45752800000001</v>
+        <v>63.34977840000001</v>
       </c>
       <c r="N72">
-        <v>-11.09086133333334</v>
+        <v>-11.98311173333333</v>
       </c>
       <c r="O72">
-        <v>-2.218172266666667</v>
+        <v>-2.396622346666666</v>
       </c>
       <c r="P72">
-        <v>-8.87268906666667</v>
+        <v>-9.586489386666665</v>
       </c>
       <c r="Q72">
-        <v>7.927310933333327</v>
+        <v>7.213510613333332</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.127736472954638</v>
+        <v>0.1305618685737635</v>
       </c>
       <c r="T72">
-        <v>1.597094366162806</v>
+        <v>1.652166585685661</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1644851095184768</v>
+        <v>0.162168417835118</v>
       </c>
       <c r="W72">
-        <v>0.1226535859226876</v>
+        <v>0.1229936762618047</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8224255475923842</v>
+        <v>0.8108420891755901</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1251884520322727</v>
+        <v>0.1659386104199861</v>
       </c>
       <c r="C73">
-        <v>-237.4012832258327</v>
+        <v>-307.6636337254577</v>
       </c>
       <c r="D73">
-        <v>189.2267167741673</v>
+        <v>125.0423662745422</v>
       </c>
       <c r="E73">
-        <v>94.83799999999997</v>
+        <v>100.9159999999999</v>
       </c>
       <c r="F73">
-        <v>431.538</v>
+        <v>437.6159999999999</v>
       </c>
       <c r="G73">
         <v>4.91</v>
@@ -7267,45 +7267,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M73">
-        <v>63.3497784</v>
+        <v>87.87329279999999</v>
       </c>
       <c r="N73">
-        <v>-11.98311173333332</v>
+        <v>-36.50662613333331</v>
       </c>
       <c r="O73">
-        <v>-2.396622346666665</v>
+        <v>-7.301325226666663</v>
       </c>
       <c r="P73">
-        <v>-9.58648938666666</v>
+        <v>-29.20530090666665</v>
       </c>
       <c r="Q73">
-        <v>7.213510613333337</v>
+        <v>-12.40530090666665</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1305618685737635</v>
+        <v>0.136661072407517</v>
       </c>
       <c r="T73">
-        <v>1.65216658568566</v>
+        <v>1.771051420847643</v>
       </c>
       <c r="U73">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.162168417835118</v>
+        <v>0.1169107587297939</v>
       </c>
       <c r="W73">
-        <v>0.1229936762618047</v>
+        <v>0.1773243196470574</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.8108420891755902</v>
+        <v>0.5845537936489695</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1659386104199861</v>
+        <v>0.1674886104199861</v>
       </c>
       <c r="C74">
-        <v>-307.6636337254577</v>
+        <v>-315.3343519515647</v>
       </c>
       <c r="D74">
-        <v>125.0423662745422</v>
+        <v>123.4496480484352</v>
       </c>
       <c r="E74">
-        <v>100.9159999999999</v>
+        <v>106.994</v>
       </c>
       <c r="F74">
-        <v>437.6159999999999</v>
+        <v>443.694</v>
       </c>
       <c r="G74">
         <v>4.91</v>
@@ -7349,37 +7349,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M74">
-        <v>87.87329279999999</v>
+        <v>89.09375519999999</v>
       </c>
       <c r="N74">
-        <v>-36.50662613333331</v>
+        <v>-37.72708853333332</v>
       </c>
       <c r="O74">
-        <v>-7.301325226666663</v>
+        <v>-7.545417706666663</v>
       </c>
       <c r="P74">
-        <v>-29.20530090666665</v>
+        <v>-30.18167082666665</v>
       </c>
       <c r="Q74">
-        <v>-12.40530090666665</v>
+        <v>-13.38167082666666</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.136661072407517</v>
+        <v>0.1400262973114991</v>
       </c>
       <c r="T74">
-        <v>1.771051420847643</v>
+        <v>1.836645917916074</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1169107587297939</v>
+        <v>0.11530924148692</v>
       </c>
       <c r="W74">
-        <v>0.1773243196470574</v>
+        <v>0.1776459043094265</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5845537936489695</v>
+        <v>0.5765462074346002</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1674886104199861</v>
+        <v>0.1690386104199861</v>
       </c>
       <c r="C75">
-        <v>-315.3343519515647</v>
+        <v>-322.9650062197602</v>
       </c>
       <c r="D75">
-        <v>123.4496480484352</v>
+        <v>121.8969937802398</v>
       </c>
       <c r="E75">
-        <v>106.994</v>
+        <v>113.0719999999999</v>
       </c>
       <c r="F75">
-        <v>443.694</v>
+        <v>449.7719999999999</v>
       </c>
       <c r="G75">
         <v>4.91</v>
@@ -7431,37 +7431,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M75">
-        <v>89.09375519999999</v>
+        <v>90.31421759999999</v>
       </c>
       <c r="N75">
-        <v>-37.72708853333332</v>
+        <v>-38.94755093333332</v>
       </c>
       <c r="O75">
-        <v>-7.545417706666663</v>
+        <v>-7.789510186666664</v>
       </c>
       <c r="P75">
-        <v>-30.18167082666665</v>
+        <v>-31.15804074666665</v>
       </c>
       <c r="Q75">
-        <v>-13.38167082666666</v>
+        <v>-14.35804074666666</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1400262973114991</v>
+        <v>0.1436503856696337</v>
       </c>
       <c r="T75">
-        <v>1.836645917916074</v>
+        <v>1.907286145528231</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.11530924148692</v>
+        <v>0.1137510084938535</v>
       </c>
       <c r="W75">
-        <v>0.1776459043094265</v>
+        <v>0.1779587974944342</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5765462074346002</v>
+        <v>0.5687550424692676</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1690386104199861</v>
+        <v>0.1705886104199861</v>
       </c>
       <c r="C76">
-        <v>-322.9650062197602</v>
+        <v>-330.5570894339533</v>
       </c>
       <c r="D76">
-        <v>121.8969937802398</v>
+        <v>120.3829105660467</v>
       </c>
       <c r="E76">
-        <v>113.0719999999999</v>
+        <v>119.15</v>
       </c>
       <c r="F76">
-        <v>449.7719999999999</v>
+        <v>455.85</v>
       </c>
       <c r="G76">
         <v>4.91</v>
@@ -7513,37 +7513,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M76">
-        <v>90.31421759999999</v>
+        <v>91.53467999999999</v>
       </c>
       <c r="N76">
-        <v>-38.94755093333332</v>
+        <v>-40.16801333333332</v>
       </c>
       <c r="O76">
-        <v>-7.789510186666664</v>
+        <v>-8.033602666666665</v>
       </c>
       <c r="P76">
-        <v>-31.15804074666665</v>
+        <v>-32.13441066666665</v>
       </c>
       <c r="Q76">
-        <v>-14.35804074666666</v>
+        <v>-15.33441066666666</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1436503856696337</v>
+        <v>0.147564401096419</v>
       </c>
       <c r="T76">
-        <v>1.907286145528231</v>
+        <v>1.98357759134936</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1137510084938535</v>
+        <v>0.1122343283806022</v>
       </c>
       <c r="W76">
-        <v>0.1779587974944342</v>
+        <v>0.1782633468611751</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5687550424692676</v>
+        <v>0.5611716419030107</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1705886104199861</v>
+        <v>0.1721386104199861</v>
       </c>
       <c r="C77">
-        <v>-330.5570894339533</v>
+        <v>-338.1120212345887</v>
       </c>
       <c r="D77">
-        <v>120.3829105660467</v>
+        <v>118.9059787654113</v>
       </c>
       <c r="E77">
-        <v>119.15</v>
+        <v>125.228</v>
       </c>
       <c r="F77">
-        <v>455.85</v>
+        <v>461.928</v>
       </c>
       <c r="G77">
         <v>4.91</v>
@@ -7595,37 +7595,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M77">
-        <v>91.53467999999999</v>
+        <v>92.7551424</v>
       </c>
       <c r="N77">
-        <v>-40.16801333333332</v>
+        <v>-41.38847573333332</v>
       </c>
       <c r="O77">
-        <v>-8.033602666666665</v>
+        <v>-8.277695146666664</v>
       </c>
       <c r="P77">
-        <v>-32.13441066666665</v>
+        <v>-33.11078058666666</v>
       </c>
       <c r="Q77">
-        <v>-15.33441066666666</v>
+        <v>-16.31078058666666</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.147564401096419</v>
+        <v>0.1518045844754365</v>
       </c>
       <c r="T77">
-        <v>1.98357759134936</v>
+        <v>2.066226657655584</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1122343283806022</v>
+        <v>0.11075756090191</v>
       </c>
       <c r="W77">
-        <v>0.1782633468611751</v>
+        <v>0.1785598817708965</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5611716419030107</v>
+        <v>0.5537878045095501</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1721386104199861</v>
+        <v>0.1736886104199861</v>
       </c>
       <c r="C78">
-        <v>-338.1120212345887</v>
+        <v>-345.631152438385</v>
       </c>
       <c r="D78">
-        <v>118.9059787654113</v>
+        <v>117.464847561615</v>
       </c>
       <c r="E78">
-        <v>125.228</v>
+        <v>131.306</v>
       </c>
       <c r="F78">
-        <v>461.928</v>
+        <v>468.006</v>
       </c>
       <c r="G78">
         <v>4.91</v>
@@ -7677,37 +7677,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M78">
-        <v>92.7551424</v>
+        <v>93.9756048</v>
       </c>
       <c r="N78">
-        <v>-41.38847573333332</v>
+        <v>-42.60893813333333</v>
       </c>
       <c r="O78">
-        <v>-8.277695146666664</v>
+        <v>-8.521787626666665</v>
       </c>
       <c r="P78">
-        <v>-33.11078058666666</v>
+        <v>-34.08715050666666</v>
       </c>
       <c r="Q78">
-        <v>-16.31078058666666</v>
+        <v>-17.28715050666666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1518045844754365</v>
+        <v>0.1564134794526294</v>
       </c>
       <c r="T78">
-        <v>2.066226657655584</v>
+        <v>2.156062599292783</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.11075756090191</v>
+        <v>0.109319151020067</v>
       </c>
       <c r="W78">
-        <v>0.1785598817708965</v>
+        <v>0.1788487144751705</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5537878045095501</v>
+        <v>0.5465957551003351</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1736886104199861</v>
+        <v>0.1752386104199861</v>
       </c>
       <c r="C79">
-        <v>-345.631152438385</v>
+        <v>-353.1157691590818</v>
       </c>
       <c r="D79">
-        <v>117.464847561615</v>
+        <v>116.0582308409182</v>
       </c>
       <c r="E79">
-        <v>131.306</v>
+        <v>137.384</v>
       </c>
       <c r="F79">
-        <v>468.006</v>
+        <v>474.084</v>
       </c>
       <c r="G79">
         <v>4.91</v>
@@ -7759,37 +7759,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M79">
-        <v>93.9756048</v>
+        <v>95.1960672</v>
       </c>
       <c r="N79">
-        <v>-42.60893813333333</v>
+        <v>-43.82940053333333</v>
       </c>
       <c r="O79">
-        <v>-8.521787626666665</v>
+        <v>-8.765880106666666</v>
       </c>
       <c r="P79">
-        <v>-34.08715050666666</v>
+        <v>-35.06352042666666</v>
       </c>
       <c r="Q79">
-        <v>-17.28715050666666</v>
+        <v>-18.26352042666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1564134794526294</v>
+        <v>0.1614413648822944</v>
       </c>
       <c r="T79">
-        <v>2.156062599292783</v>
+        <v>2.254065444715182</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.109319151020067</v>
+        <v>0.1079176234428867</v>
       </c>
       <c r="W79">
-        <v>0.1788487144751705</v>
+        <v>0.1791301412126683</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5465957551003351</v>
+        <v>0.5395881172144333</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1752386104199861</v>
+        <v>0.1767886104199861</v>
       </c>
       <c r="C80">
-        <v>-353.1157691590818</v>
+        <v>-360.5670966356207</v>
       </c>
       <c r="D80">
-        <v>116.0582308409182</v>
+        <v>114.6849033643793</v>
       </c>
       <c r="E80">
-        <v>137.384</v>
+        <v>143.462</v>
       </c>
       <c r="F80">
-        <v>474.084</v>
+        <v>480.162</v>
       </c>
       <c r="G80">
         <v>4.91</v>
@@ -7841,37 +7841,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M80">
-        <v>95.1960672</v>
+        <v>96.4165296</v>
       </c>
       <c r="N80">
-        <v>-43.82940053333333</v>
+        <v>-45.04986293333333</v>
       </c>
       <c r="O80">
-        <v>-8.765880106666666</v>
+        <v>-9.009972586666667</v>
       </c>
       <c r="P80">
-        <v>-35.06352042666666</v>
+        <v>-36.03989034666667</v>
       </c>
       <c r="Q80">
-        <v>-18.26352042666667</v>
+        <v>-19.23989034666667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1614413648822944</v>
+        <v>0.166948096543356</v>
       </c>
       <c r="T80">
-        <v>2.254065444715182</v>
+        <v>2.361401894463524</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1079176234428867</v>
+        <v>0.106551577576521</v>
       </c>
       <c r="W80">
-        <v>0.1791301412126683</v>
+        <v>0.1794044432226346</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5395881172144333</v>
+        <v>0.5327578878826051</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1767886104199861</v>
+        <v>0.1783386104199861</v>
       </c>
       <c r="C81">
-        <v>-360.5670966356207</v>
+        <v>-367.9863027917098</v>
       </c>
       <c r="D81">
-        <v>114.6849033643793</v>
+        <v>113.3436972082902</v>
       </c>
       <c r="E81">
-        <v>143.462</v>
+        <v>149.54</v>
       </c>
       <c r="F81">
-        <v>480.162</v>
+        <v>486.24</v>
       </c>
       <c r="G81">
         <v>4.91</v>
@@ -7923,37 +7923,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M81">
-        <v>96.4165296</v>
+        <v>97.63699200000001</v>
       </c>
       <c r="N81">
-        <v>-45.04986293333333</v>
+        <v>-46.27032533333333</v>
       </c>
       <c r="O81">
-        <v>-9.009972586666667</v>
+        <v>-9.254065066666668</v>
       </c>
       <c r="P81">
-        <v>-36.03989034666667</v>
+        <v>-37.01626026666666</v>
       </c>
       <c r="Q81">
-        <v>-19.23989034666667</v>
+        <v>-20.21626026666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.166948096543356</v>
+        <v>0.1730055013705238</v>
       </c>
       <c r="T81">
-        <v>2.361401894463524</v>
+        <v>2.479471989186701</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.106551577576521</v>
+        <v>0.1052196828568145</v>
       </c>
       <c r="W81">
-        <v>0.1794044432226346</v>
+        <v>0.1796718876823516</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5327578878826051</v>
+        <v>0.5260984142840726</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1783386104199861</v>
+        <v>0.1798886104199861</v>
       </c>
       <c r="C82">
-        <v>-367.9863027917098</v>
+        <v>-375.3745015485064</v>
       </c>
       <c r="D82">
-        <v>113.3436972082902</v>
+        <v>112.0334984514936</v>
       </c>
       <c r="E82">
-        <v>149.54</v>
+        <v>155.618</v>
       </c>
       <c r="F82">
-        <v>486.24</v>
+        <v>492.318</v>
       </c>
       <c r="G82">
         <v>4.91</v>
@@ -8005,37 +8005,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M82">
-        <v>97.63699200000001</v>
+        <v>98.85745439999999</v>
       </c>
       <c r="N82">
-        <v>-46.27032533333333</v>
+        <v>-47.49078773333332</v>
       </c>
       <c r="O82">
-        <v>-9.254065066666668</v>
+        <v>-9.498157546666665</v>
       </c>
       <c r="P82">
-        <v>-37.01626026666666</v>
+        <v>-37.99263018666666</v>
       </c>
       <c r="Q82">
-        <v>-20.21626026666667</v>
+        <v>-21.19263018666666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1730055013705238</v>
+        <v>0.1797005277584461</v>
       </c>
       <c r="T82">
-        <v>2.479471989186701</v>
+        <v>2.609970514933369</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1052196828568145</v>
+        <v>0.1039206744264835</v>
       </c>
       <c r="W82">
-        <v>0.1796718876823516</v>
+        <v>0.1799327285751621</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5260984142840726</v>
+        <v>0.5196033721324174</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1798886104199861</v>
+        <v>0.1814386104199861</v>
       </c>
       <c r="C83">
-        <v>-375.3745015485064</v>
+        <v>-382.7327559101674</v>
       </c>
       <c r="D83">
-        <v>112.0334984514936</v>
+        <v>110.7532440898326</v>
       </c>
       <c r="E83">
-        <v>155.618</v>
+        <v>161.696</v>
       </c>
       <c r="F83">
-        <v>492.318</v>
+        <v>498.396</v>
       </c>
       <c r="G83">
         <v>4.91</v>
@@ -8087,37 +8087,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M83">
-        <v>98.85745439999999</v>
+        <v>100.0779168</v>
       </c>
       <c r="N83">
-        <v>-47.49078773333332</v>
+        <v>-48.71125013333334</v>
       </c>
       <c r="O83">
-        <v>-9.498157546666665</v>
+        <v>-9.742250026666667</v>
       </c>
       <c r="P83">
-        <v>-37.99263018666666</v>
+        <v>-38.96900010666667</v>
       </c>
       <c r="Q83">
-        <v>-21.19263018666666</v>
+        <v>-22.16900010666667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1797005277584461</v>
+        <v>0.1871394459672487</v>
       </c>
       <c r="T83">
-        <v>2.609970514933369</v>
+        <v>2.754968876874112</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1039206744264835</v>
+        <v>0.1026533491285995</v>
       </c>
       <c r="W83">
-        <v>0.1799327285751621</v>
+        <v>0.1801872074949772</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5196033721324174</v>
+        <v>0.5132667456429976</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1814386104199861</v>
+        <v>0.1829886104199861</v>
       </c>
       <c r="C84">
-        <v>-382.7327559101674</v>
+        <v>-390.0620808402305</v>
       </c>
       <c r="D84">
-        <v>110.7532440898326</v>
+        <v>109.5019191597695</v>
       </c>
       <c r="E84">
-        <v>161.696</v>
+        <v>167.774</v>
       </c>
       <c r="F84">
-        <v>498.396</v>
+        <v>504.474</v>
       </c>
       <c r="G84">
         <v>4.91</v>
@@ -8169,37 +8169,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M84">
-        <v>100.0779168</v>
+        <v>101.2983792</v>
       </c>
       <c r="N84">
-        <v>-48.71125013333334</v>
+        <v>-49.93171253333333</v>
       </c>
       <c r="O84">
-        <v>-9.742250026666667</v>
+        <v>-9.986342506666666</v>
       </c>
       <c r="P84">
-        <v>-38.96900010666667</v>
+        <v>-39.94537002666666</v>
       </c>
       <c r="Q84">
-        <v>-22.16900010666667</v>
+        <v>-23.14537002666666</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1871394459672487</v>
+        <v>0.1954535310241457</v>
       </c>
       <c r="T84">
-        <v>2.754968876874112</v>
+        <v>2.917025869631413</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1026533491285995</v>
+        <v>0.1014165617897007</v>
       </c>
       <c r="W84">
-        <v>0.1801872074949772</v>
+        <v>0.1804355543926281</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5132667456429976</v>
+        <v>0.5070828089485037</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1829886104199861</v>
+        <v>0.1845386104199861</v>
       </c>
       <c r="C85">
-        <v>-390.0620808402305</v>
+        <v>-397.3634459451847</v>
       </c>
       <c r="D85">
-        <v>109.5019191597695</v>
+        <v>108.2785540548153</v>
       </c>
       <c r="E85">
-        <v>167.774</v>
+        <v>173.852</v>
       </c>
       <c r="F85">
-        <v>504.474</v>
+        <v>510.552</v>
       </c>
       <c r="G85">
         <v>4.91</v>
@@ -8251,37 +8251,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M85">
-        <v>101.2983792</v>
+        <v>102.5188416</v>
       </c>
       <c r="N85">
-        <v>-49.93171253333333</v>
+        <v>-51.15217493333333</v>
       </c>
       <c r="O85">
-        <v>-9.986342506666666</v>
+        <v>-10.23043498666667</v>
       </c>
       <c r="P85">
-        <v>-39.94537002666666</v>
+        <v>-40.92173994666666</v>
       </c>
       <c r="Q85">
-        <v>-23.14537002666666</v>
+        <v>-24.12173994666666</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1954535310241457</v>
+        <v>0.2048068767131548</v>
       </c>
       <c r="T85">
-        <v>2.917025869631413</v>
+        <v>3.099339986483377</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1014165617897007</v>
+        <v>0.1002092217683948</v>
       </c>
       <c r="W85">
-        <v>0.1804355543926281</v>
+        <v>0.1806779882689064</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5070828089485037</v>
+        <v>0.5010461088419738</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1845386104199861</v>
+        <v>0.2161856947189896</v>
       </c>
       <c r="C86">
-        <v>-397.3634459451846</v>
+        <v>-423.5528792060488</v>
       </c>
       <c r="D86">
-        <v>108.2785540548154</v>
+        <v>88.16712079395114</v>
       </c>
       <c r="E86">
-        <v>173.852</v>
+        <v>179.93</v>
       </c>
       <c r="F86">
-        <v>510.552</v>
+        <v>516.63</v>
       </c>
       <c r="G86">
         <v>4.91</v>
@@ -8333,45 +8333,45 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M86">
-        <v>102.5188416</v>
+        <v>121.821354</v>
       </c>
       <c r="N86">
-        <v>-51.15217493333333</v>
+        <v>-70.45468733333333</v>
       </c>
       <c r="O86">
-        <v>-10.23043498666667</v>
+        <v>-14.09093746666667</v>
       </c>
       <c r="P86">
-        <v>-40.92173994666666</v>
+        <v>-56.36374986666666</v>
       </c>
       <c r="Q86">
-        <v>-24.12173994666666</v>
+        <v>-39.56374986666666</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2048068767131547</v>
+        <v>0.2177212304873883</v>
       </c>
       <c r="T86">
-        <v>3.099339986483375</v>
+        <v>3.351064779017227</v>
       </c>
       <c r="U86">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1002092217683948</v>
+        <v>0.08433113732534392</v>
       </c>
       <c r="W86">
-        <v>0.1806779882689064</v>
+        <v>0.2159147178186839</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.5010461088419738</v>
+        <v>0.4216556866267196</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2161856947189896</v>
+        <v>0.2180856947189896</v>
       </c>
       <c r="C87">
-        <v>-423.5528792060488</v>
+        <v>-430.6032032854319</v>
       </c>
       <c r="D87">
-        <v>88.16712079395114</v>
+        <v>87.19479671456806</v>
       </c>
       <c r="E87">
-        <v>179.93</v>
+        <v>186.008</v>
       </c>
       <c r="F87">
-        <v>516.63</v>
+        <v>522.708</v>
       </c>
       <c r="G87">
         <v>4.91</v>
@@ -8415,37 +8415,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M87">
-        <v>121.821354</v>
+        <v>123.2545464</v>
       </c>
       <c r="N87">
-        <v>-70.45468733333333</v>
+        <v>-71.88787973333332</v>
       </c>
       <c r="O87">
-        <v>-14.09093746666667</v>
+        <v>-14.37757594666667</v>
       </c>
       <c r="P87">
-        <v>-56.36374986666666</v>
+        <v>-57.51030378666665</v>
       </c>
       <c r="Q87">
-        <v>-39.56374986666666</v>
+        <v>-40.71030378666666</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2177212304873883</v>
+        <v>0.2300013183793446</v>
       </c>
       <c r="T87">
-        <v>3.351064779017227</v>
+        <v>3.590426548947029</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08433113732534392</v>
+        <v>0.08335054270528179</v>
       </c>
       <c r="W87">
-        <v>0.2159147178186839</v>
+        <v>0.2161459420300946</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4216556866267196</v>
+        <v>0.416752713526409</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2180856947189896</v>
+        <v>0.2199856947189896</v>
       </c>
       <c r="C88">
-        <v>-430.6032032854319</v>
+        <v>-437.6323153387204</v>
       </c>
       <c r="D88">
-        <v>87.19479671456806</v>
+        <v>86.24368466127947</v>
       </c>
       <c r="E88">
-        <v>186.008</v>
+        <v>192.086</v>
       </c>
       <c r="F88">
-        <v>522.708</v>
+        <v>528.7859999999999</v>
       </c>
       <c r="G88">
         <v>4.91</v>
@@ -8497,37 +8497,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M88">
-        <v>123.2545464</v>
+        <v>124.6877388</v>
       </c>
       <c r="N88">
-        <v>-71.88787973333332</v>
+        <v>-73.32107213333332</v>
       </c>
       <c r="O88">
-        <v>-14.37757594666667</v>
+        <v>-14.66421442666666</v>
       </c>
       <c r="P88">
-        <v>-57.51030378666665</v>
+        <v>-58.65685770666666</v>
       </c>
       <c r="Q88">
-        <v>-40.71030378666666</v>
+        <v>-41.85685770666666</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2300013183793446</v>
+        <v>0.2441706505623711</v>
       </c>
       <c r="T88">
-        <v>3.590426548947029</v>
+        <v>3.866613206558339</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08335054270528179</v>
+        <v>0.08239249049027855</v>
       </c>
       <c r="W88">
-        <v>0.2161459420300946</v>
+        <v>0.2163718507423923</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.416752713526409</v>
+        <v>0.4119624524513927</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2199856947189896</v>
+        <v>0.2218856947189896</v>
       </c>
       <c r="C89">
-        <v>-437.6323153387204</v>
+        <v>-444.6409020119759</v>
       </c>
       <c r="D89">
-        <v>86.24368466127947</v>
+        <v>85.31309798802398</v>
       </c>
       <c r="E89">
-        <v>192.086</v>
+        <v>198.1639999999999</v>
       </c>
       <c r="F89">
-        <v>528.7859999999999</v>
+        <v>534.8639999999999</v>
       </c>
       <c r="G89">
         <v>4.91</v>
@@ -8579,37 +8579,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M89">
-        <v>124.6877388</v>
+        <v>126.1209312</v>
       </c>
       <c r="N89">
-        <v>-73.32107213333332</v>
+        <v>-74.75426453333331</v>
       </c>
       <c r="O89">
-        <v>-14.66421442666666</v>
+        <v>-14.95085290666666</v>
       </c>
       <c r="P89">
-        <v>-58.65685770666666</v>
+        <v>-59.80341162666665</v>
       </c>
       <c r="Q89">
-        <v>-41.85685770666666</v>
+        <v>-43.00341162666665</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2441706505623711</v>
+        <v>0.2607015381092354</v>
       </c>
       <c r="T89">
-        <v>3.866613206558339</v>
+        <v>4.188830973771534</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08239249049027855</v>
+        <v>0.08145621218925267</v>
       </c>
       <c r="W89">
-        <v>0.2163718507423923</v>
+        <v>0.2165926251657742</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4119624524513927</v>
+        <v>0.4072810609462633</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2218856947189896</v>
+        <v>0.2237856947189896</v>
       </c>
       <c r="C90">
-        <v>-444.6409020119759</v>
+        <v>-451.6296206314312</v>
       </c>
       <c r="D90">
-        <v>85.31309798802398</v>
+        <v>84.40237936856877</v>
       </c>
       <c r="E90">
-        <v>198.1639999999999</v>
+        <v>204.242</v>
       </c>
       <c r="F90">
-        <v>534.8639999999999</v>
+        <v>540.942</v>
       </c>
       <c r="G90">
         <v>4.91</v>
@@ -8661,37 +8661,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M90">
-        <v>126.1209312</v>
+        <v>127.5541236</v>
       </c>
       <c r="N90">
-        <v>-74.75426453333331</v>
+        <v>-76.18745693333334</v>
       </c>
       <c r="O90">
-        <v>-14.95085290666666</v>
+        <v>-15.23749138666667</v>
       </c>
       <c r="P90">
-        <v>-59.80341162666665</v>
+        <v>-60.94996554666667</v>
       </c>
       <c r="Q90">
-        <v>-43.00341162666665</v>
+        <v>-44.14996554666667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2607015381092354</v>
+        <v>0.2802380415737113</v>
       </c>
       <c r="T90">
-        <v>4.188830973771534</v>
+        <v>4.569633789568946</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08145621218925267</v>
+        <v>0.08054097385004756</v>
       </c>
       <c r="W90">
-        <v>0.2165926251657742</v>
+        <v>0.2168084383661588</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4072810609462633</v>
+        <v>0.4027048692502377</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2237856947189896</v>
+        <v>0.2256856947189896</v>
       </c>
       <c r="C91">
-        <v>-451.6296206314312</v>
+        <v>-458.5991007519088</v>
       </c>
       <c r="D91">
-        <v>84.40237936856877</v>
+        <v>83.51089924809119</v>
       </c>
       <c r="E91">
-        <v>204.242</v>
+        <v>210.32</v>
       </c>
       <c r="F91">
-        <v>540.942</v>
+        <v>547.02</v>
       </c>
       <c r="G91">
         <v>4.91</v>
@@ -8743,37 +8743,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M91">
-        <v>127.5541236</v>
+        <v>128.987316</v>
       </c>
       <c r="N91">
-        <v>-76.18745693333334</v>
+        <v>-77.62064933333332</v>
       </c>
       <c r="O91">
-        <v>-15.23749138666667</v>
+        <v>-15.52412986666666</v>
       </c>
       <c r="P91">
-        <v>-60.94996554666667</v>
+        <v>-62.09651946666666</v>
       </c>
       <c r="Q91">
-        <v>-44.14996554666667</v>
+        <v>-45.29651946666666</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2802380415737113</v>
+        <v>0.3036818457310825</v>
       </c>
       <c r="T91">
-        <v>4.569633789568946</v>
+        <v>5.026597168525841</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08054097385004756</v>
+        <v>0.0796460741406026</v>
       </c>
       <c r="W91">
-        <v>0.2168084383661588</v>
+        <v>0.2170194557176459</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4027048692502377</v>
+        <v>0.3982303707030129</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2256856947189896</v>
+        <v>0.2275856947189896</v>
       </c>
       <c r="C92">
-        <v>-458.5991007519088</v>
+        <v>-465.5499456081371</v>
       </c>
       <c r="D92">
-        <v>83.51089924809119</v>
+        <v>82.63805439186284</v>
       </c>
       <c r="E92">
-        <v>210.32</v>
+        <v>216.398</v>
       </c>
       <c r="F92">
-        <v>547.02</v>
+        <v>553.098</v>
       </c>
       <c r="G92">
         <v>4.91</v>
@@ -8825,37 +8825,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M92">
-        <v>128.987316</v>
+        <v>130.4205084</v>
       </c>
       <c r="N92">
-        <v>-77.62064933333332</v>
+        <v>-79.05384173333331</v>
       </c>
       <c r="O92">
-        <v>-15.52412986666666</v>
+        <v>-15.81076834666666</v>
       </c>
       <c r="P92">
-        <v>-62.09651946666666</v>
+        <v>-63.24307338666665</v>
       </c>
       <c r="Q92">
-        <v>-45.29651946666666</v>
+        <v>-46.44307338666665</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3036818457310825</v>
+        <v>0.3323353841456473</v>
       </c>
       <c r="T92">
-        <v>5.026597168525841</v>
+        <v>5.585107965028714</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0796460741406026</v>
+        <v>0.07877084255663994</v>
       </c>
       <c r="W92">
-        <v>0.2170194557176459</v>
+        <v>0.2172258353251443</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3982303707030129</v>
+        <v>0.3938542127831997</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2275856947189896</v>
+        <v>0.2294856947189896</v>
       </c>
       <c r="C93">
-        <v>-465.5499456081371</v>
+        <v>-472.4827334759934</v>
       </c>
       <c r="D93">
-        <v>82.63805439186284</v>
+        <v>81.78326652400658</v>
       </c>
       <c r="E93">
-        <v>216.398</v>
+        <v>222.4759999999999</v>
       </c>
       <c r="F93">
-        <v>553.098</v>
+        <v>559.1759999999999</v>
       </c>
       <c r="G93">
         <v>4.91</v>
@@ -8907,37 +8907,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M93">
-        <v>130.4205084</v>
+        <v>131.8537008</v>
       </c>
       <c r="N93">
-        <v>-79.05384173333331</v>
+        <v>-80.48703413333331</v>
       </c>
       <c r="O93">
-        <v>-15.81076834666666</v>
+        <v>-16.09740682666666</v>
       </c>
       <c r="P93">
-        <v>-63.24307338666665</v>
+        <v>-64.38962730666665</v>
       </c>
       <c r="Q93">
-        <v>-46.44307338666665</v>
+        <v>-47.58962730666666</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3323353841456473</v>
+        <v>0.3681523071638533</v>
       </c>
       <c r="T93">
-        <v>5.585107965028714</v>
+        <v>6.283246460657304</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07877084255663994</v>
+        <v>0.07791463774624169</v>
       </c>
       <c r="W93">
-        <v>0.2172258353251443</v>
+        <v>0.2174277284194362</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3938542127831997</v>
+        <v>0.3895731887312084</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2294856947189896</v>
+        <v>0.2313856947189896</v>
       </c>
       <c r="C94">
-        <v>-472.4827334759934</v>
+        <v>-479.3980189501293</v>
       </c>
       <c r="D94">
-        <v>81.78326652400658</v>
+        <v>80.94598104987075</v>
       </c>
       <c r="E94">
-        <v>222.4759999999999</v>
+        <v>228.554</v>
       </c>
       <c r="F94">
-        <v>559.1759999999999</v>
+        <v>565.254</v>
       </c>
       <c r="G94">
         <v>4.91</v>
@@ -8989,37 +8989,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M94">
-        <v>131.8537008</v>
+        <v>133.2868932</v>
       </c>
       <c r="N94">
-        <v>-80.48703413333331</v>
+        <v>-81.92022653333333</v>
       </c>
       <c r="O94">
-        <v>-16.09740682666666</v>
+        <v>-16.38404530666667</v>
       </c>
       <c r="P94">
-        <v>-64.38962730666665</v>
+        <v>-65.53618122666667</v>
       </c>
       <c r="Q94">
-        <v>-47.58962730666666</v>
+        <v>-48.73618122666667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3681523071638533</v>
+        <v>0.4142026367586895</v>
       </c>
       <c r="T94">
-        <v>6.283246460657304</v>
+        <v>7.180853097894063</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07791463774624169</v>
+        <v>0.07707684594251864</v>
       </c>
       <c r="W94">
-        <v>0.2174277284194362</v>
+        <v>0.2176252797267541</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3895731887312084</v>
+        <v>0.3853842297125931</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2313856947189896</v>
+        <v>0.2332856947189896</v>
       </c>
       <c r="C95">
-        <v>-479.3980189501293</v>
+        <v>-486.2963341439112</v>
       </c>
       <c r="D95">
-        <v>80.94598104987075</v>
+        <v>80.12566585608883</v>
       </c>
       <c r="E95">
-        <v>228.554</v>
+        <v>234.632</v>
       </c>
       <c r="F95">
-        <v>565.254</v>
+        <v>571.332</v>
       </c>
       <c r="G95">
         <v>4.91</v>
@@ -9071,37 +9071,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M95">
-        <v>133.2868932</v>
+        <v>134.7200856</v>
       </c>
       <c r="N95">
-        <v>-81.92022653333333</v>
+        <v>-83.35341893333333</v>
       </c>
       <c r="O95">
-        <v>-16.38404530666667</v>
+        <v>-16.67068378666667</v>
       </c>
       <c r="P95">
-        <v>-65.53618122666667</v>
+        <v>-66.68273514666666</v>
       </c>
       <c r="Q95">
-        <v>-48.73618122666667</v>
+        <v>-49.88273514666666</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4142026367586895</v>
+        <v>0.4756030762184711</v>
       </c>
       <c r="T95">
-        <v>7.180853097894063</v>
+        <v>8.377661947543075</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07707684594251864</v>
+        <v>0.07625687949632164</v>
       </c>
       <c r="W95">
-        <v>0.2176252797267541</v>
+        <v>0.2178186278147674</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3853842297125931</v>
+        <v>0.3812843974816081</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2332856947189896</v>
+        <v>0.2351856947189896</v>
       </c>
       <c r="C96">
-        <v>-486.2963341439112</v>
+        <v>-493.1781898171312</v>
       </c>
       <c r="D96">
-        <v>80.12566585608883</v>
+        <v>79.32181018286883</v>
       </c>
       <c r="E96">
-        <v>234.632</v>
+        <v>240.71</v>
       </c>
       <c r="F96">
-        <v>571.332</v>
+        <v>577.41</v>
       </c>
       <c r="G96">
         <v>4.91</v>
@@ -9153,37 +9153,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M96">
-        <v>134.7200856</v>
+        <v>136.153278</v>
       </c>
       <c r="N96">
-        <v>-83.35341893333333</v>
+        <v>-84.78661133333333</v>
       </c>
       <c r="O96">
-        <v>-16.67068378666667</v>
+        <v>-16.95732226666667</v>
       </c>
       <c r="P96">
-        <v>-66.68273514666666</v>
+        <v>-67.82928906666666</v>
       </c>
       <c r="Q96">
-        <v>-49.88273514666666</v>
+        <v>-51.02928906666666</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4756030762184711</v>
+        <v>0.5615636914621657</v>
       </c>
       <c r="T96">
-        <v>8.377661947543075</v>
+        <v>10.0531943370517</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07625687949632164</v>
+        <v>0.07545417550162352</v>
       </c>
       <c r="W96">
-        <v>0.2178186278147674</v>
+        <v>0.2180079054167172</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3812843974816081</v>
+        <v>0.3772708775081175</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2351856947189896</v>
+        <v>0.2370856947189896</v>
       </c>
       <c r="C97">
-        <v>-493.1781898171312</v>
+        <v>-500.0440764365089</v>
       </c>
       <c r="D97">
-        <v>79.32181018286883</v>
+        <v>78.53392356349117</v>
       </c>
       <c r="E97">
-        <v>240.71</v>
+        <v>246.7880000000001</v>
       </c>
       <c r="F97">
-        <v>577.41</v>
+        <v>583.4880000000001</v>
       </c>
       <c r="G97">
         <v>4.91</v>
@@ -9235,37 +9235,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M97">
-        <v>136.153278</v>
+        <v>137.5864704</v>
       </c>
       <c r="N97">
-        <v>-84.78661133333333</v>
+        <v>-86.21980373333335</v>
       </c>
       <c r="O97">
-        <v>-16.95732226666667</v>
+        <v>-17.24396074666667</v>
       </c>
       <c r="P97">
-        <v>-67.82928906666666</v>
+        <v>-68.97584298666668</v>
       </c>
       <c r="Q97">
-        <v>-51.02928906666666</v>
+        <v>-52.17584298666668</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5615636914621657</v>
+        <v>0.6905046143277073</v>
       </c>
       <c r="T97">
-        <v>10.0531943370517</v>
+        <v>12.56649292131462</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07545417550162352</v>
+        <v>0.07466819450681492</v>
       </c>
       <c r="W97">
-        <v>0.2180079054167172</v>
+        <v>0.218193239735293</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3772708775081175</v>
+        <v>0.3733409725340746</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2370856947189895</v>
+        <v>0.2389856947189896</v>
       </c>
       <c r="C98">
-        <v>-500.0440764365088</v>
+        <v>-506.8944651736132</v>
       </c>
       <c r="D98">
-        <v>78.53392356349117</v>
+        <v>77.76153482638675</v>
       </c>
       <c r="E98">
-        <v>246.788</v>
+        <v>252.8659999999999</v>
       </c>
       <c r="F98">
-        <v>583.4879999999999</v>
+        <v>589.5659999999999</v>
       </c>
       <c r="G98">
         <v>4.91</v>
@@ -9317,37 +9317,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M98">
-        <v>137.5864704</v>
+        <v>139.0196628</v>
       </c>
       <c r="N98">
-        <v>-86.21980373333332</v>
+        <v>-87.65299613333332</v>
       </c>
       <c r="O98">
-        <v>-17.24396074666667</v>
+        <v>-17.53059922666666</v>
       </c>
       <c r="P98">
-        <v>-68.97584298666666</v>
+        <v>-70.12239690666665</v>
       </c>
       <c r="Q98">
-        <v>-52.17584298666667</v>
+        <v>-53.32239690666665</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6905046143277056</v>
+        <v>0.9054061524369408</v>
       </c>
       <c r="T98">
-        <v>12.56649292131459</v>
+        <v>16.75532389508612</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07466819450681493</v>
+        <v>0.07389841930571375</v>
       </c>
       <c r="W98">
-        <v>0.218193239735293</v>
+        <v>0.2183747527277127</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3733409725340746</v>
+        <v>0.3694920965285687</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2389856947189896</v>
+        <v>0.2408856947189896</v>
       </c>
       <c r="C99">
-        <v>-506.8944651736132</v>
+        <v>-513.72980884447</v>
       </c>
       <c r="D99">
-        <v>77.76153482638675</v>
+        <v>77.00419115552994</v>
       </c>
       <c r="E99">
-        <v>252.8659999999999</v>
+        <v>258.9439999999999</v>
       </c>
       <c r="F99">
-        <v>589.5659999999999</v>
+        <v>595.6439999999999</v>
       </c>
       <c r="G99">
         <v>4.91</v>
@@ -9399,37 +9399,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M99">
-        <v>139.0196628</v>
+        <v>140.4528552</v>
       </c>
       <c r="N99">
-        <v>-87.65299613333332</v>
+        <v>-89.08618853333331</v>
       </c>
       <c r="O99">
-        <v>-17.53059922666666</v>
+        <v>-17.81723770666666</v>
       </c>
       <c r="P99">
-        <v>-70.12239690666665</v>
+        <v>-71.26895082666665</v>
       </c>
       <c r="Q99">
-        <v>-53.32239690666665</v>
+        <v>-54.46895082666666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9054061524369408</v>
+        <v>1.335209228655411</v>
       </c>
       <c r="T99">
-        <v>16.75532389508612</v>
+        <v>25.13298584262918</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07389841930571375</v>
+        <v>0.07314435380259422</v>
       </c>
       <c r="W99">
-        <v>0.2183747527277127</v>
+        <v>0.2185525613733483</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3694920965285687</v>
+        <v>0.3657217690129712</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2408856947189896</v>
+        <v>0.2427856947189896</v>
       </c>
       <c r="C100">
-        <v>-513.72980884447</v>
+        <v>-520.5505427947918</v>
       </c>
       <c r="D100">
-        <v>77.00419115552994</v>
+        <v>76.26145720520819</v>
       </c>
       <c r="E100">
-        <v>258.9439999999999</v>
+        <v>265.022</v>
       </c>
       <c r="F100">
-        <v>595.6439999999999</v>
+        <v>601.722</v>
       </c>
       <c r="G100">
         <v>4.91</v>
@@ -9481,37 +9481,37 @@
         <v>51.36666666666667</v>
       </c>
       <c r="M100">
-        <v>140.4528552</v>
+        <v>141.8860476</v>
       </c>
       <c r="N100">
-        <v>-89.08618853333331</v>
+        <v>-90.51938093333334</v>
       </c>
       <c r="O100">
-        <v>-17.81723770666666</v>
+        <v>-18.10387618666667</v>
       </c>
       <c r="P100">
-        <v>-71.26895082666665</v>
+        <v>-72.41550474666667</v>
       </c>
       <c r="Q100">
-        <v>-54.46895082666666</v>
+        <v>-55.61550474666667</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.335209228655411</v>
+        <v>2.624618457310822</v>
       </c>
       <c r="T100">
-        <v>25.13298584262918</v>
+        <v>50.26597168525836</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07314435380259422</v>
+        <v>0.07240552194600235</v>
       </c>
       <c r="W100">
-        <v>0.2185525613733483</v>
+        <v>0.2187267779251326</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3657217690129712</v>
+        <v>0.3620276097300118</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2427856947189896</v>
-      </c>
-      <c r="C101">
-        <v>-520.5505427947918</v>
-      </c>
-      <c r="D101">
-        <v>76.26145720520819</v>
-      </c>
-      <c r="E101">
-        <v>265.022</v>
-      </c>
-      <c r="F101">
-        <v>601.722</v>
-      </c>
-      <c r="G101">
-        <v>4.91</v>
-      </c>
-      <c r="H101">
-        <v>271.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>68.16666666666667</v>
-      </c>
-      <c r="K101">
-        <v>16.8</v>
-      </c>
-      <c r="L101">
-        <v>51.36666666666667</v>
-      </c>
-      <c r="M101">
-        <v>141.8860476</v>
-      </c>
-      <c r="N101">
-        <v>-90.51938093333334</v>
-      </c>
-      <c r="O101">
-        <v>-18.10387618666667</v>
-      </c>
-      <c r="P101">
-        <v>-72.41550474666667</v>
-      </c>
-      <c r="Q101">
-        <v>-55.61550474666667</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.624618457310822</v>
-      </c>
-      <c r="T101">
-        <v>50.26597168525836</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07240552194600235</v>
-      </c>
-      <c r="W101">
-        <v>0.2187267779251326</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3620276097300118</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
